--- a/data/FRMPL (TRY).xlsx
+++ b/data/FRMPL (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>597165676</v>
+        <v>564413413</v>
       </c>
       <c r="C3">
-        <v>40193162</v>
+        <v>639047302.298753</v>
       </c>
       <c r="D3">
-        <v>94985243.61663926</v>
+        <v>43012184</v>
       </c>
       <c r="E3">
-        <v>43190924.69480089</v>
+        <v>101646940.08870524</v>
       </c>
       <c r="F3">
-        <v>75186122.80806719</v>
+        <v>46220077.64224061</v>
       </c>
       <c r="G3">
-        <v>140975671.92511925</v>
+        <v>80459227.45030323</v>
+      </c>
+      <c r="H3">
+        <v>150862861.77221867</v>
       </c>
     </row>
     <row r="4">
@@ -474,8 +481,8 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
-      <c r="F5">
-        <v>230876.49269723988</v>
+      <c r="G5">
+        <v>247068.7880298882</v>
       </c>
     </row>
     <row r="6">
@@ -488,22 +495,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>1292767240</v>
+        <v>1383163731</v>
       </c>
       <c r="C7">
-        <v>1986581404</v>
+        <v>1383434196.6134782</v>
       </c>
       <c r="D7">
-        <v>1679617298.7376056</v>
+        <v>2125913980</v>
       </c>
       <c r="E7">
-        <v>1167714967.9625313</v>
+        <v>1797415603.0571752</v>
       </c>
       <c r="F7">
-        <v>1520503199.647828</v>
+        <v>1249611506.6907</v>
       </c>
       <c r="G7">
-        <v>1982240288.4623933</v>
+        <v>1627142193.4029021</v>
+      </c>
+      <c r="H7">
+        <v>2121262757.9917946</v>
       </c>
     </row>
     <row r="8">
@@ -521,22 +531,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>7621698</v>
+        <v>36652060</v>
       </c>
       <c r="C10">
-        <v>10057641</v>
+        <v>8156238.279568837</v>
       </c>
       <c r="D10">
-        <v>7061516.190632035</v>
+        <v>10763052</v>
       </c>
       <c r="E10">
-        <v>3640686.9024864323</v>
+        <v>7556768.670948142</v>
       </c>
       <c r="F10">
-        <v>17776304.84265952</v>
+        <v>3896022.891222499</v>
       </c>
       <c r="G10">
-        <v>30092468.079721548</v>
+        <v>19023028.467801332</v>
+      </c>
+      <c r="H10">
+        <v>32202973.678375635</v>
       </c>
     </row>
     <row r="11">
@@ -559,22 +572,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>1606773401</v>
+        <v>2067437906</v>
       </c>
       <c r="C14">
-        <v>1408444099</v>
+        <v>1719462870.3248553</v>
       </c>
       <c r="D14">
-        <v>1514288011.262638</v>
+        <v>1507227941</v>
       </c>
       <c r="E14">
-        <v>1203477797.380683</v>
+        <v>1620491108.9041438</v>
       </c>
       <c r="F14">
-        <v>1202697510.812694</v>
+        <v>1287882526.9129682</v>
       </c>
       <c r="G14">
-        <v>943286041.6542964</v>
+        <v>1287047515.71535</v>
+      </c>
+      <c r="H14">
+        <v>1009442478.7657208</v>
       </c>
     </row>
     <row r="15">
@@ -592,22 +608,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>293387499</v>
+        <v>266219940</v>
       </c>
       <c r="C17">
-        <v>106505346</v>
+        <v>313963942.1675805</v>
       </c>
       <c r="D17">
-        <v>80216760.48221381</v>
+        <v>113975296</v>
       </c>
       <c r="E17">
-        <v>62921008.81889768</v>
+        <v>85842683.94103742</v>
       </c>
       <c r="F17">
-        <v>89998315.50843129</v>
+        <v>67333911.77632354</v>
       </c>
       <c r="G17">
-        <v>67462476.11109461</v>
+        <v>96310258.69124977</v>
+      </c>
+      <c r="H17">
+        <v>72193890.40234973</v>
       </c>
     </row>
     <row r="18">
@@ -630,22 +649,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>19485260</v>
+        <v>41163456</v>
       </c>
       <c r="C21">
-        <v>310218</v>
+        <v>20851839.511267893</v>
       </c>
       <c r="D21">
-        <v>21571035.39118917</v>
+        <v>331976</v>
       </c>
       <c r="E21">
-        <v>21827126.496905122</v>
+        <v>23083898.70440304</v>
       </c>
       <c r="F21">
-        <v>7858969.161302201</v>
+        <v>23357950.507491745</v>
       </c>
       <c r="G21">
-        <v>27295416.440885954</v>
+        <v>8410150.219985627</v>
+      </c>
+      <c r="H21">
+        <v>29209753.578786064</v>
       </c>
     </row>
     <row r="22">
@@ -663,22 +685,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>3817200774</v>
+        <v>4359050506</v>
       </c>
       <c r="C24">
-        <v>3552091870</v>
+        <v>4084916389.1955037</v>
       </c>
       <c r="D24">
-        <v>3397739865.6809177</v>
+        <v>3801224429</v>
       </c>
       <c r="E24">
-        <v>2502772512.2563043</v>
+        <v>3636037003.3664126</v>
       </c>
       <c r="F24">
-        <v>2914251299.2736797</v>
+        <v>2678301996.4209466</v>
       </c>
       <c r="G24">
-        <v>3191352362.6735106</v>
+        <v>3118639442.735622</v>
+      </c>
+      <c r="H24">
+        <v>3415174716.189245</v>
       </c>
     </row>
     <row r="25">
@@ -714,19 +739,22 @@
         <v>268423</v>
       </c>
       <c r="C30">
-        <v>295378</v>
+        <v>287248.5826277433</v>
       </c>
       <c r="D30">
-        <v>274139.3513046371</v>
+        <v>316095</v>
       </c>
       <c r="E30">
-        <v>343851.0762435719</v>
+        <v>293365.8445988086</v>
       </c>
       <c r="F30">
-        <v>849979.5517489205</v>
+        <v>367966.73267935356</v>
       </c>
       <c r="G30">
-        <v>244476.37682123532</v>
+        <v>909592.0301257418</v>
+      </c>
+      <c r="H30">
+        <v>261622.48662695044</v>
       </c>
     </row>
     <row r="31">
@@ -764,22 +792,25 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
-        <v>605306129</v>
+        <v>647760398</v>
       </c>
       <c r="C37">
-        <v>265168207</v>
+        <v>647758677.9491174</v>
       </c>
       <c r="D37">
-        <v>258979023.1596391</v>
+        <v>283766272</v>
       </c>
       <c r="E37">
-        <v>258977522.52639967</v>
+        <v>277142261.7768367</v>
       </c>
       <c r="F37">
-        <v>258268333.61419806</v>
+        <v>277140655.8981636</v>
       </c>
       <c r="G37">
-        <v>97879216.96618575</v>
+        <v>276381728.72036874</v>
+      </c>
+      <c r="H37">
+        <v>104743879.40768944</v>
       </c>
     </row>
     <row r="38">
@@ -792,36 +823,39 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>894347624</v>
+        <v>1016663542</v>
       </c>
       <c r="C39">
-        <v>888461524</v>
+        <v>957071813.4082769</v>
       </c>
       <c r="D39">
-        <v>898351295.307702</v>
+        <v>950775423</v>
       </c>
       <c r="E39">
-        <v>947490633.2380879</v>
+        <v>961356278.258326</v>
       </c>
       <c r="F39">
-        <v>852793304.9595453</v>
+        <v>1013941955.2374562</v>
       </c>
       <c r="G39">
-        <v>817831139.0148549</v>
+        <v>912603123.145402</v>
+      </c>
+      <c r="H39">
+        <v>875188920.1404126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
-      <c r="E40">
-        <v>17466122.0330348</v>
-      </c>
       <c r="F40">
-        <v>30492784.452717673</v>
+        <v>18691091.292446792</v>
       </c>
       <c r="G40">
-        <v>34759329.81090038</v>
+        <v>32631365.84576001</v>
+      </c>
+      <c r="H40">
+        <v>37197141.15881053</v>
       </c>
     </row>
     <row r="41">
@@ -829,22 +863,25 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>5528423</v>
+        <v>7394089</v>
       </c>
       <c r="C41">
-        <v>7791434</v>
+        <v>5916153.499948278</v>
       </c>
       <c r="D41">
-        <v>7412996.772684885</v>
+        <v>8337900</v>
       </c>
       <c r="E41">
-        <v>8427721.960681528</v>
+        <v>7932899.997309354</v>
       </c>
       <c r="F41">
-        <v>7701611.0492097335</v>
+        <v>9018791.93655713</v>
       </c>
       <c r="G41">
-        <v>7874549.945545584</v>
+        <v>8241755.951746546</v>
+      </c>
+      <c r="H41">
+        <v>8426823.747180168</v>
       </c>
     </row>
     <row r="42">
@@ -852,16 +889,19 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>64011</v>
+        <v>89098274</v>
       </c>
       <c r="C42">
-        <v>340137921</v>
+        <v>68500.34841494386</v>
       </c>
       <c r="D42">
-        <v>335793030.1639037</v>
+        <v>363994133</v>
       </c>
       <c r="E42">
-        <v>335395927.3639207</v>
+        <v>359343543.4774829</v>
+      </c>
+      <c r="F42">
+        <v>358918590.2638886</v>
       </c>
     </row>
     <row r="43">
@@ -889,22 +929,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>1505514610</v>
+        <v>1761184726</v>
       </c>
       <c r="C47">
-        <v>1501854464</v>
+        <v>1611102393.7883852</v>
       </c>
       <c r="D47">
-        <v>1500810484.7552342</v>
+        <v>1607189823</v>
       </c>
       <c r="E47">
-        <v>1568101778.198368</v>
+        <v>1606068349.3545537</v>
       </c>
       <c r="F47">
-        <v>1150106013.6274197</v>
+        <v>1678079051.3611915</v>
       </c>
       <c r="G47">
-        <v>958588712.114308</v>
+        <v>1230767565.693403</v>
+      </c>
+      <c r="H47">
+        <v>1025818386.9407198</v>
       </c>
     </row>
     <row r="48">
@@ -912,22 +955,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>5322715384</v>
+        <v>6120235232</v>
       </c>
       <c r="C48">
-        <v>5053946334</v>
+        <v>5696018782.983889</v>
       </c>
       <c r="D48">
-        <v>4898550350.4361515</v>
+        <v>5408414252</v>
       </c>
       <c r="E48">
-        <v>4070874290.4546723</v>
+        <v>5242105352.720965</v>
       </c>
       <c r="F48">
-        <v>4064357312.901099</v>
+        <v>4356381047.782138</v>
       </c>
       <c r="G48">
-        <v>4149941074.787819</v>
+        <v>4349407008.429025</v>
+      </c>
+      <c r="H48">
+        <v>4440993103.129965</v>
       </c>
     </row>
     <row r="49">
@@ -940,22 +986,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>577511210</v>
+        <v>524344545</v>
       </c>
       <c r="C50">
-        <v>1043183289</v>
+        <v>618014389.6913939</v>
       </c>
       <c r="D50">
-        <v>1124015719.4017737</v>
+        <v>1116348886</v>
       </c>
       <c r="E50">
-        <v>879605938.6106259</v>
+        <v>1202847454.3890157</v>
       </c>
       <c r="F50">
-        <v>405866987.1906498</v>
+        <v>941296234.4391057</v>
       </c>
       <c r="G50">
-        <v>607127562.4045414</v>
+        <v>434332068.4364105</v>
+      </c>
+      <c r="H50">
+        <v>649707855.7908275</v>
       </c>
     </row>
     <row r="51">
@@ -968,22 +1017,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>314560076</v>
+        <v>781321626</v>
       </c>
       <c r="C52">
-        <v>541806646</v>
+        <v>336621436.9941295</v>
       </c>
       <c r="D52">
-        <v>444108183.61105007</v>
+        <v>579807261</v>
       </c>
       <c r="E52">
-        <v>271068165.4169221</v>
+        <v>475255273.488694</v>
       </c>
       <c r="F52">
-        <v>271920322.8755947</v>
+        <v>290079264.114899</v>
       </c>
       <c r="G52">
-        <v>272686044.69722205</v>
+        <v>290991186.79730463</v>
+      </c>
+      <c r="H52">
+        <v>291810611.7644259</v>
       </c>
     </row>
     <row r="53">
@@ -996,22 +1048,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>58041556</v>
+        <v>52944372</v>
       </c>
       <c r="C54">
-        <v>53349390</v>
+        <v>62112243.3416987</v>
       </c>
       <c r="D54">
-        <v>57298239.890509084</v>
+        <v>57091149</v>
       </c>
       <c r="E54">
-        <v>54700159.59954125</v>
+        <v>61316795.48925821</v>
       </c>
       <c r="F54">
-        <v>38762191.525365144</v>
+        <v>58536501.396972574</v>
       </c>
       <c r="G54">
-        <v>14555674.747512786</v>
+        <v>41480739.63559852</v>
+      </c>
+      <c r="H54">
+        <v>15576522.65421921</v>
       </c>
     </row>
     <row r="55">
@@ -1019,30 +1074,39 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>140190006</v>
+        <v>139813590</v>
       </c>
       <c r="C55">
-        <v>175979</v>
+        <v>150022093.94155803</v>
       </c>
       <c r="D55">
-        <v>145191.36614180243</v>
+        <v>188322</v>
       </c>
       <c r="E55">
-        <v>162384.8790194287</v>
+        <v>155374.21954906423</v>
       </c>
       <c r="F55">
-        <v>116922.48600329054</v>
+        <v>173773.5825115898</v>
       </c>
       <c r="G55">
-        <v>18639523.69729332</v>
+        <v>125122.72935537329</v>
+      </c>
+      <c r="H55">
+        <v>19946788.32627509</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
-      <c r="E56">
-        <v>206639281.2868148</v>
+      <c r="B56">
+        <v>468744361</v>
+      </c>
+      <c r="D56">
+        <v>683199870</v>
+      </c>
+      <c r="F56">
+        <v>221131723.67812413</v>
       </c>
     </row>
     <row r="57">
@@ -1064,20 +1128,17 @@
       <c r="A60" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
-      <c r="B60">
-        <v>461901600</v>
-      </c>
       <c r="C60">
-        <v>638422889</v>
-      </c>
-      <c r="D60">
-        <v>422057847.33027834</v>
-      </c>
-      <c r="F60">
-        <v>661190356.2153587</v>
+        <v>494296613.6042248</v>
+      </c>
+      <c r="E60">
+        <v>451658458.5990728</v>
       </c>
       <c r="G60">
-        <v>890196409.5256087</v>
+        <v>707562290.3774807</v>
+      </c>
+      <c r="H60">
+        <v>952629457.5969169</v>
       </c>
     </row>
     <row r="61">
@@ -1085,22 +1146,25 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
-        <v>18487388</v>
+        <v>32399670</v>
       </c>
       <c r="C61">
-        <v>7833454</v>
+        <v>19783982.74175145</v>
       </c>
       <c r="D61">
-        <v>11304714.487755477</v>
+        <v>8382868</v>
       </c>
       <c r="E61">
-        <v>2394740.6481970022</v>
+        <v>12097559.499815874</v>
       </c>
       <c r="F61">
-        <v>50825210.65569223</v>
+        <v>2562693.424019671</v>
       </c>
       <c r="G61">
-        <v>19303093.083546665</v>
+        <v>54389786.72693498</v>
+      </c>
+      <c r="H61">
+        <v>20656896.497618217</v>
       </c>
     </row>
     <row r="62">
@@ -1108,22 +1172,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>8545192</v>
+        <v>5961371</v>
       </c>
       <c r="C62">
-        <v>8019263</v>
+        <v>9144500.621339941</v>
       </c>
       <c r="D62">
-        <v>7239099.005856464</v>
+        <v>8581709</v>
       </c>
       <c r="E62">
-        <v>3502960.280579532</v>
+        <v>7746806.081945939</v>
       </c>
       <c r="F62">
-        <v>4334410.422098942</v>
+        <v>3748636.948390237</v>
       </c>
       <c r="G62">
-        <v>3826907.2565558534</v>
+        <v>4638400.026357055</v>
+      </c>
+      <c r="H62">
+        <v>4095303.626341612</v>
       </c>
     </row>
     <row r="63">
@@ -1146,22 +1213,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>1579237028</v>
+        <v>2005529535</v>
       </c>
       <c r="C66">
-        <v>2292790910</v>
+        <v>1689995260.9360962</v>
       </c>
       <c r="D66">
-        <v>2066168995.0933647</v>
+        <v>2453600065</v>
       </c>
       <c r="E66">
-        <v>1418073630.7217</v>
+        <v>2211077721.767351</v>
       </c>
       <c r="F66">
-        <v>1433016401.3707628</v>
+        <v>1517528827.584023</v>
       </c>
       <c r="G66">
-        <v>1826335215.4122808</v>
+        <v>1533519594.7294416</v>
+      </c>
+      <c r="H66">
+        <v>1954423436.2566245</v>
       </c>
     </row>
     <row r="67">
@@ -1173,23 +1243,23 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
-      <c r="B68">
-        <v>1182553</v>
-      </c>
       <c r="C68">
-        <v>6221270</v>
+        <v>1265490.1894851995</v>
       </c>
       <c r="D68">
-        <v>36658627.18049905</v>
+        <v>6657610</v>
       </c>
       <c r="E68">
-        <v>33345883.353573125</v>
+        <v>39229643.87804777</v>
       </c>
       <c r="F68">
-        <v>35773227.986267604</v>
+        <v>35684564.026867814</v>
       </c>
       <c r="G68">
-        <v>88339049.26095118</v>
+        <v>38282148.08371298</v>
+      </c>
+      <c r="H68">
+        <v>94534621.44037813</v>
       </c>
     </row>
     <row r="69">
@@ -1252,22 +1322,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>32090589</v>
+        <v>33172291</v>
       </c>
       <c r="C80">
-        <v>31742135</v>
+        <v>34341230.84064872</v>
       </c>
       <c r="D80">
-        <v>29948338.935382895</v>
+        <v>33968429</v>
       </c>
       <c r="E80">
-        <v>39756487.69476389</v>
+        <v>32048736.178509276</v>
       </c>
       <c r="F80">
-        <v>25690204.077185337</v>
+        <v>42544769.78715775</v>
       </c>
       <c r="G80">
-        <v>15829984.923444265</v>
+        <v>27491961.227573495</v>
+      </c>
+      <c r="H80">
+        <v>16940205.31876147</v>
       </c>
     </row>
     <row r="81">
@@ -1280,22 +1353,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>112261223</v>
+        <v>121262669</v>
       </c>
       <c r="C82">
-        <v>79315831</v>
+        <v>120134553.2640907</v>
       </c>
       <c r="D82">
-        <v>156619661.23665813</v>
+        <v>84878794</v>
       </c>
       <c r="E82">
-        <v>98033500.91499117</v>
+        <v>167604026.8600953</v>
       </c>
       <c r="F82">
-        <v>251043026.2665641</v>
+        <v>104908983.90922831</v>
       </c>
       <c r="G82">
-        <v>242462769.45709518</v>
+        <v>268649681.56100583</v>
+      </c>
+      <c r="H82">
+        <v>259467656.89433423</v>
       </c>
     </row>
     <row r="83">
@@ -1308,22 +1384,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>145534365</v>
+        <v>154434960</v>
       </c>
       <c r="C84">
-        <v>117279236</v>
+        <v>155741274.29422462</v>
       </c>
       <c r="D84">
-        <v>223226627.35254008</v>
+        <v>125504833</v>
       </c>
       <c r="E84">
-        <v>171135871.96332818</v>
+        <v>238882406.91665235</v>
       </c>
       <c r="F84">
-        <v>312506458.33001703</v>
+        <v>183138317.72325388</v>
       </c>
       <c r="G84">
-        <v>346631803.6414906</v>
+        <v>334423790.8722923</v>
+      </c>
+      <c r="H84">
+        <v>370942483.6534738</v>
       </c>
     </row>
     <row r="85">
@@ -1336,22 +1415,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>3597943991</v>
+        <v>3960270737</v>
       </c>
       <c r="C86">
-        <v>2643876188</v>
+        <v>3850282247.753568</v>
       </c>
       <c r="D86">
-        <v>2609154727.9902472</v>
+        <v>2829309354</v>
       </c>
       <c r="E86">
-        <v>2481664787.7696443</v>
+        <v>2792145224.0369625</v>
       </c>
       <c r="F86">
-        <v>2318834453.20032</v>
+        <v>2655713902.474861</v>
       </c>
       <c r="G86">
-        <v>1976974055.7340477</v>
+        <v>2481463622.8272915</v>
+      </c>
+      <c r="H86">
+        <v>2115627183.219867</v>
       </c>
     </row>
     <row r="87">
@@ -1362,7 +1444,7 @@
         <v>160000000</v>
       </c>
       <c r="C87">
-        <v>130000000</v>
+        <v>160000000</v>
       </c>
       <c r="D87">
         <v>130000000</v>
@@ -1374,6 +1456,9 @@
         <v>130000000</v>
       </c>
       <c r="G87">
+        <v>130000000</v>
+      </c>
+      <c r="H87">
         <v>80000000</v>
       </c>
     </row>
@@ -1382,22 +1467,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>718811943</v>
+        <v>780448348</v>
       </c>
       <c r="C88">
-        <v>717323486</v>
+        <v>780446552.7286527</v>
       </c>
       <c r="D88">
-        <v>717330465.8847417</v>
+        <v>776752092</v>
       </c>
       <c r="E88">
-        <v>717325058.014588</v>
+        <v>776757153.2346239</v>
       </c>
       <c r="F88">
-        <v>717330465.8847417</v>
+        <v>776751366.0888253</v>
       </c>
       <c r="G88">
-        <v>652983135.1081307</v>
+        <v>776757153.2346239</v>
+      </c>
+      <c r="H88">
+        <v>704390185.0804522</v>
       </c>
     </row>
     <row r="89">
@@ -1430,7 +1518,13 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>889820319</v>
+        <v>952230239</v>
+      </c>
+      <c r="C94">
+        <v>952226990.3328568</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1447,56 +1541,62 @@
       <c r="A97" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
-      <c r="B97">
-        <v>-29916445</v>
-      </c>
       <c r="C97">
-        <v>-32920654</v>
-      </c>
-      <c r="E97">
-        <v>-15992233.256586043</v>
+        <v>-32014605.393393405</v>
+      </c>
+      <c r="F97">
+        <v>-17113832.77888482</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
+      <c r="B98">
+        <v>-29916444</v>
+      </c>
+      <c r="D98">
+        <v>-35229605</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>9440762</v>
+        <v>10102908</v>
       </c>
       <c r="C99">
-        <v>9440762</v>
+        <v>10102880.540884571</v>
       </c>
       <c r="D99">
-        <v>9440834.46394355</v>
+        <v>10102908</v>
       </c>
       <c r="E99">
-        <v>9440779.295733763</v>
+        <v>10102958.087015403</v>
       </c>
       <c r="F99">
-        <v>9440834.46394355</v>
+        <v>10102899.04963758</v>
       </c>
       <c r="G99">
-        <v>60127.495797720374</v>
+        <v>10102958.087015403</v>
+      </c>
+      <c r="H99">
+        <v>64344.47847185513</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>-22927631.58390601</v>
-      </c>
-      <c r="F100">
-        <v>4709896.068555068</v>
+      <c r="E100">
+        <v>-24535638.43444147</v>
       </c>
       <c r="G100">
-        <v>2138251.341391415</v>
+        <v>5040219.98866127</v>
+      </c>
+      <c r="H100">
+        <v>2288215.4924002592</v>
       </c>
     </row>
     <row r="101">
@@ -1514,22 +1614,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>1820032594</v>
+        <v>1947683959</v>
       </c>
       <c r="C103">
-        <v>1640888139</v>
+        <v>1947678786.701568</v>
       </c>
       <c r="D103">
-        <v>1640888986.9201953</v>
+        <v>1755974875</v>
       </c>
       <c r="E103">
-        <v>1457358267.3487408</v>
+        <v>1755971119.2494671</v>
       </c>
       <c r="F103">
-        <v>1118064502.895623</v>
+        <v>1559568653.493738</v>
       </c>
       <c r="G103">
-        <v>900955237.3194207</v>
+        <v>1196478855.1769412</v>
+      </c>
+      <c r="H103">
+        <v>964142845.1773719</v>
       </c>
     </row>
     <row r="104">
@@ -1537,31 +1640,31 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>29754818</v>
+        <v>139721727</v>
       </c>
       <c r="C104">
-        <v>179144455</v>
+        <v>31841642.842999533</v>
       </c>
       <c r="D104">
-        <v>134422072.3052726</v>
+        <v>191709084</v>
       </c>
       <c r="E104">
-        <v>183532916.36716783</v>
+        <v>143849631.9002976</v>
       </c>
       <c r="F104">
-        <v>339288753.8874561</v>
+        <v>196404816.62154552</v>
       </c>
       <c r="G104">
-        <v>340837304.469307</v>
+        <v>363084436.3400491</v>
+      </c>
+      <c r="H104">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
       <c r="C105">
         <v>0</v>
       </c>
@@ -1571,22 +1674,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>3597943991</v>
+        <v>3960270737</v>
       </c>
       <c r="C106">
-        <v>2643876188</v>
+        <v>3850282247.753568</v>
       </c>
       <c r="D106">
-        <v>2609154727.9902472</v>
+        <v>2829309354</v>
       </c>
       <c r="E106">
-        <v>2481664787.7696443</v>
+        <v>2792145224.0369625</v>
       </c>
       <c r="F106">
-        <v>2318834453.20032</v>
+        <v>2655713902.474861</v>
       </c>
       <c r="G106">
-        <v>1976974055.7340477</v>
+        <v>2481463622.8272915</v>
+      </c>
+      <c r="H106">
+        <v>2115627183.219867</v>
       </c>
     </row>
     <row r="107">
@@ -1594,39 +1700,45 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>5322715384</v>
+        <v>6120235232</v>
       </c>
       <c r="C107">
-        <v>5053946334</v>
+        <v>5696018782.983889</v>
       </c>
       <c r="D107">
-        <v>4898550350.4361515</v>
+        <v>5408414252</v>
       </c>
       <c r="E107">
-        <v>4070874290.4546723</v>
+        <v>5242105352.720965</v>
       </c>
       <c r="F107">
-        <v>4064357312.901099</v>
+        <v>4356381047.782138</v>
       </c>
       <c r="G107">
-        <v>4149941074.787819</v>
+        <v>4349407008.429025</v>
+      </c>
+      <c r="H107">
+        <v>4440993103.129965</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="C108">
+        <v>-99302438.46298175</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1637,6 +1749,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1644,27 +1758,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1678,28 +1798,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>809806419</v>
+        <v>1769257408</v>
       </c>
       <c r="C3">
-        <v>3802275826.4354343</v>
+        <v>866598143</v>
       </c>
       <c r="D3">
-        <v>2811769321.35583</v>
+        <v>4068944695.1390524</v>
       </c>
       <c r="E3">
-        <v>966719615</v>
+        <v>3008969992.2720256</v>
       </c>
       <c r="F3">
-        <v>4064186427.0770974</v>
+        <v>1943501155</v>
       </c>
       <c r="G3">
-        <v>2898097565.221506</v>
+        <v>1034515662</v>
       </c>
       <c r="H3">
-        <v>4012712256.490779</v>
+        <v>4349224137.696131</v>
       </c>
       <c r="I3">
-        <v>4518659110.91694</v>
+        <v>3101352782.461978</v>
+      </c>
+      <c r="J3">
+        <v>4294139876.8732553</v>
+      </c>
+      <c r="K3">
+        <v>4835570815.425018</v>
       </c>
     </row>
     <row r="4">
@@ -1722,28 +1848,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-561216857</v>
+        <v>-1210571136</v>
       </c>
       <c r="C7">
-        <v>-2747788726.140967</v>
+        <v>-600574995</v>
       </c>
       <c r="D7">
-        <v>-2049207111.2098765</v>
+        <v>-2940502181.051866</v>
       </c>
       <c r="E7">
-        <v>-709681041</v>
+        <v>-2192926232.8702435</v>
       </c>
       <c r="F7">
-        <v>-3003524301.8925686</v>
+        <v>-1418767957</v>
       </c>
       <c r="G7">
-        <v>-1989642499.9516454</v>
+        <v>-759450972</v>
       </c>
       <c r="H7">
-        <v>-2757778661.0180564</v>
+        <v>-3214173519.432472</v>
       </c>
       <c r="I7">
-        <v>-3249249911.5504003</v>
+        <v>-2129184116.2904444</v>
+      </c>
+      <c r="J7">
+        <v>-2951192750.1684747</v>
+      </c>
+      <c r="K7">
+        <v>-3477132852.610144</v>
       </c>
     </row>
     <row r="8">
@@ -1751,28 +1883,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>248589562</v>
+        <v>558686272</v>
       </c>
       <c r="C8">
-        <v>1054487100.2944673</v>
+        <v>266023148</v>
       </c>
       <c r="D8">
-        <v>762562210.1459541</v>
+        <v>1128442514.087186</v>
       </c>
       <c r="E8">
-        <v>257038574</v>
+        <v>816043759.4017825</v>
       </c>
       <c r="F8">
-        <v>1060662125.1845287</v>
+        <v>524733198</v>
       </c>
       <c r="G8">
-        <v>908455065.2698605</v>
+        <v>275064690</v>
       </c>
       <c r="H8">
-        <v>1254933595.4727223</v>
+        <v>1135050618.263658</v>
       </c>
       <c r="I8">
-        <v>1269409199.3665397</v>
+        <v>972168666.1715332</v>
+      </c>
+      <c r="J8">
+        <v>1342947126.7047803</v>
+      </c>
+      <c r="K8">
+        <v>1358437962.8148742</v>
       </c>
     </row>
     <row r="9">
@@ -1800,28 +1938,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>248589562</v>
+        <v>558686272</v>
       </c>
       <c r="C13">
-        <v>1054487100.2944673</v>
+        <v>266023148</v>
       </c>
       <c r="D13">
-        <v>762562210.1459541</v>
+        <v>1128442514.087186</v>
       </c>
       <c r="E13">
-        <v>257038574</v>
+        <v>816043759.4017825</v>
       </c>
       <c r="F13">
-        <v>1060662125.1845287</v>
+        <v>524733198</v>
       </c>
       <c r="G13">
-        <v>908455065.2698605</v>
+        <v>275064690</v>
       </c>
       <c r="H13">
-        <v>1254933595.4727223</v>
+        <v>1135050618.263658</v>
       </c>
       <c r="I13">
-        <v>1269409199.3665397</v>
+        <v>972168666.1715332</v>
+      </c>
+      <c r="J13">
+        <v>1342947126.7047803</v>
+      </c>
+      <c r="K13">
+        <v>1358437962.8148742</v>
       </c>
     </row>
     <row r="14"/>
@@ -1830,28 +1974,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-43858955</v>
+        <v>-75568515</v>
       </c>
       <c r="C15">
-        <v>-132356529.33028257</v>
+        <v>-46934784</v>
       </c>
       <c r="D15">
-        <v>-94097392.69965135</v>
+        <v>-141639224.1039367</v>
       </c>
       <c r="E15">
-        <v>-31886855</v>
+        <v>-100696820.62245415</v>
       </c>
       <c r="F15">
-        <v>-130686036.95100275</v>
+        <v>-68129236</v>
       </c>
       <c r="G15">
-        <v>-87795953.05239336</v>
+        <v>-34123080</v>
       </c>
       <c r="H15">
-        <v>-92019073.63491544</v>
+        <v>-139851573.3875727</v>
       </c>
       <c r="I15">
-        <v>-50948886.57566776</v>
+        <v>-93953435.71434596</v>
+      </c>
+      <c r="J15">
+        <v>-98472740.69788134</v>
+      </c>
+      <c r="K15">
+        <v>-54522136.53570008</v>
       </c>
     </row>
     <row r="16">
@@ -1859,28 +2009,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-64602917</v>
+        <v>-150550286</v>
       </c>
       <c r="C16">
-        <v>-263284462.15493459</v>
+        <v>-69133520</v>
       </c>
       <c r="D16">
-        <v>-189073849.15819576</v>
+        <v>-281749658.493917</v>
       </c>
       <c r="E16">
-        <v>-63677659</v>
+        <v>-202334357.27438956</v>
       </c>
       <c r="F16">
-        <v>-265063845.69693813</v>
+        <v>-135809200</v>
       </c>
       <c r="G16">
-        <v>-190509932.84387714</v>
+        <v>-68143372</v>
       </c>
       <c r="H16">
-        <v>-196074806.07422146</v>
+        <v>-283653837.3474119</v>
       </c>
       <c r="I16">
-        <v>-183281415.86387584</v>
+        <v>-203871159.27439255</v>
+      </c>
+      <c r="J16">
+        <v>-209826319.40567592</v>
+      </c>
+      <c r="K16">
+        <v>-196135677.37825865</v>
       </c>
     </row>
     <row r="17">
@@ -1893,28 +2049,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>20982412</v>
+        <v>56663169</v>
       </c>
       <c r="C18">
-        <v>182909724.2560368</v>
+        <v>22453908</v>
       </c>
       <c r="D18">
-        <v>160934522.18418756</v>
+        <v>195737917.54573166</v>
       </c>
       <c r="E18">
-        <v>49881464</v>
+        <v>172221506.328746</v>
       </c>
       <c r="F18">
-        <v>156119464.3624323</v>
+        <v>102548311</v>
       </c>
       <c r="G18">
-        <v>121046687.89811179</v>
+        <v>53379650</v>
       </c>
       <c r="H18">
-        <v>322213901.2797679</v>
+        <v>167068749.17093974</v>
       </c>
       <c r="I18">
-        <v>315769092.6944779</v>
+        <v>129536178.08651054</v>
+      </c>
+      <c r="J18">
+        <v>344812055.7685777</v>
+      </c>
+      <c r="K18">
+        <v>337915246.8832301</v>
       </c>
     </row>
     <row r="19">
@@ -1922,28 +2084,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-13225414</v>
+        <v>-42342590</v>
       </c>
       <c r="C19">
-        <v>-46228621.03399955</v>
+        <v>-14152913</v>
       </c>
       <c r="D19">
-        <v>-36631613.4446101</v>
+        <v>-49470819.82114592</v>
       </c>
       <c r="E19">
-        <v>-15276783</v>
+        <v>-39200735.56040889</v>
       </c>
       <c r="F19">
-        <v>-99386646.98332608</v>
+        <v>-29963924</v>
       </c>
       <c r="G19">
-        <v>-87753103.59902827</v>
+        <v>-16348144</v>
       </c>
       <c r="H19">
-        <v>-289443993.4779848</v>
+        <v>-106357031.54381068</v>
       </c>
       <c r="I19">
-        <v>-165278392.69624794</v>
+        <v>-93907581.0567887</v>
+      </c>
+      <c r="J19">
+        <v>-309743862.7713158</v>
+      </c>
+      <c r="K19">
+        <v>-176870029.91915292</v>
       </c>
     </row>
     <row r="20">
@@ -1956,28 +2124,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>147884688</v>
+        <v>346888050</v>
       </c>
       <c r="C21">
-        <v>795527212.0312874</v>
+        <v>158255839</v>
       </c>
       <c r="D21">
-        <v>603693877.0276846</v>
+        <v>851320729.2139181</v>
       </c>
       <c r="E21">
-        <v>196078741</v>
+        <v>646033352.273276</v>
       </c>
       <c r="F21">
-        <v>721645059.9156941</v>
+        <v>393379149</v>
       </c>
       <c r="G21">
-        <v>663442763.6726736</v>
+        <v>209829744</v>
       </c>
       <c r="H21">
-        <v>999609623.5653684</v>
+        <v>772256925.1558027</v>
       </c>
       <c r="I21">
-        <v>1185669596.9252262</v>
+        <v>709972668.2125167</v>
+      </c>
+      <c r="J21">
+        <v>1069716259.5984849</v>
+      </c>
+      <c r="K21">
+        <v>1268825365.8649926</v>
       </c>
     </row>
     <row r="22"/>
@@ -1996,36 +2170,42 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>53121037</v>
+        <v>96878900</v>
       </c>
       <c r="C25">
-        <v>12509767.236112889</v>
+        <v>56846415</v>
       </c>
       <c r="D25">
-        <v>3522738.6077892147</v>
+        <v>13387127.435340524</v>
       </c>
       <c r="E25">
-        <v>197057</v>
+        <v>3769802.4090911793</v>
       </c>
       <c r="F25">
-        <v>8855445.004106583</v>
+        <v>2169348</v>
       </c>
       <c r="G25">
-        <v>6864133.560996906</v>
+        <v>210876</v>
       </c>
       <c r="H25">
-        <v>165081138.68157706</v>
+        <v>9476512.914197167</v>
       </c>
       <c r="I25">
-        <v>438544.87443053914</v>
+        <v>7345542.805064714</v>
+      </c>
+      <c r="J25">
+        <v>176658941.6885175</v>
+      </c>
+      <c r="K25">
+        <v>469301.787100338</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="I26">
-        <v>-5417.905370008493</v>
+      <c r="K26">
+        <v>-5797.884824870368</v>
       </c>
     </row>
     <row r="27">
@@ -2063,28 +2243,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>201005725</v>
+        <v>443766950</v>
       </c>
       <c r="C33">
-        <v>808036979.2674004</v>
+        <v>215102254</v>
       </c>
       <c r="D33">
-        <v>607216615.6354738</v>
+        <v>864707856.6492587</v>
       </c>
       <c r="E33">
-        <v>196275798</v>
+        <v>649803154.6823672</v>
       </c>
       <c r="F33">
-        <v>730500504.9198006</v>
+        <v>395548497</v>
       </c>
       <c r="G33">
-        <v>670306897.2336705</v>
+        <v>210040620</v>
       </c>
       <c r="H33">
-        <v>1164690762.2469456</v>
+        <v>781733438.0699998</v>
       </c>
       <c r="I33">
-        <v>1186102723.8942866</v>
+        <v>717318211.0175813</v>
+      </c>
+      <c r="J33">
+        <v>1246375201.2870026</v>
+      </c>
+      <c r="K33">
+        <v>1269288869.7672682</v>
       </c>
     </row>
     <row r="34"/>
@@ -2098,28 +2284,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-81716670</v>
+        <v>-107687961</v>
       </c>
       <c r="C36">
-        <v>-552949190.059564</v>
+        <v>-87447460</v>
       </c>
       <c r="D36">
-        <v>-465350310.3464163</v>
+        <v>-591729736.6834005</v>
       </c>
       <c r="E36">
-        <v>-191284637</v>
+        <v>-497987195.85277176</v>
       </c>
       <c r="F36">
-        <v>-260230800.89275357</v>
+        <v>-327288401</v>
       </c>
       <c r="G36">
-        <v>-234415356.40617484</v>
+        <v>-204699429</v>
       </c>
       <c r="H36">
-        <v>-179406726.9997446</v>
+        <v>-278481831.7078862</v>
       </c>
       <c r="I36">
-        <v>-278392905.4030803</v>
+        <v>-250855846.45820594</v>
+      </c>
+      <c r="J36">
+        <v>-191989241.02837357</v>
+      </c>
+      <c r="K36">
+        <v>-297917717.52291805</v>
       </c>
     </row>
     <row r="37">
@@ -2127,28 +2319,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-21527539</v>
+        <v>-77090920</v>
       </c>
       <c r="C37">
-        <v>-38320727.44164126</v>
+        <v>-23037265</v>
       </c>
       <c r="D37">
-        <v>94229282.75212193</v>
+        <v>-41008313.903337345</v>
       </c>
       <c r="E37">
-        <v>98546929</v>
+        <v>100837960.65380344</v>
       </c>
       <c r="F37">
-        <v>-270467252.4504492</v>
+        <v>124964162</v>
       </c>
       <c r="G37">
-        <v>-512309031.3419497</v>
+        <v>105458025</v>
       </c>
       <c r="H37">
-        <v>-469053156.98645175</v>
+        <v>-289436206.7096023</v>
       </c>
       <c r="I37">
-        <v>-340669584.8141553</v>
+        <v>-548239320.476886</v>
+      </c>
+      <c r="J37">
+        <v>-501949737.9934903</v>
+      </c>
+      <c r="K37">
+        <v>-364562110.4832592</v>
       </c>
     </row>
     <row r="38">
@@ -2156,28 +2354,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>97761516</v>
+        <v>258988069</v>
       </c>
       <c r="C38">
-        <v>216767061.76619512</v>
+        <v>104617529</v>
       </c>
       <c r="D38">
-        <v>236095588.04117936</v>
+        <v>231969806.06252086</v>
       </c>
       <c r="E38">
-        <v>103538090</v>
+        <v>252653919.4833988</v>
       </c>
       <c r="F38">
-        <v>199802451.57659787</v>
+        <v>193224258</v>
       </c>
       <c r="G38">
-        <v>-76417490.51445407</v>
+        <v>110799216</v>
       </c>
       <c r="H38">
-        <v>516230878.2607492</v>
+        <v>213815399.65251136</v>
       </c>
       <c r="I38">
-        <v>567040233.6770511</v>
+        <v>-81776955.9175106</v>
+      </c>
+      <c r="J38">
+        <v>552436222.2651386</v>
+      </c>
+      <c r="K38">
+        <v>606809041.7610908</v>
       </c>
     </row>
     <row r="39"/>
@@ -2186,28 +2390,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-68006698</v>
+        <v>-119266342</v>
       </c>
       <c r="C40">
-        <v>-37622274.165805794</v>
+        <v>-72776008</v>
       </c>
       <c r="D40">
-        <v>-101673515.73590676</v>
+        <v>-40260875.29518736</v>
       </c>
       <c r="E40">
-        <v>-63538425</v>
+        <v>-108804287.5831012</v>
       </c>
       <c r="F40">
-        <v>-16269535.20943006</v>
+        <v>-99625242</v>
       </c>
       <c r="G40">
-        <v>175090985.26937947</v>
+        <v>-67994374</v>
       </c>
       <c r="H40">
-        <v>-176942124.3732931</v>
+        <v>-17410583.03096586</v>
       </c>
       <c r="I40">
-        <v>-226202929.20774406</v>
+        <v>187370819.00405082</v>
+      </c>
+      <c r="J40">
+        <v>-189351785.92508957</v>
+      </c>
+      <c r="K40">
+        <v>-242067448.76992002</v>
       </c>
     </row>
     <row r="41">
@@ -2215,28 +2425,34 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-27823255</v>
+        <v>-70081453</v>
       </c>
       <c r="C41">
-        <v>-33202776.768303894</v>
+        <v>-29774500</v>
       </c>
       <c r="D41">
-        <v>-23212245.016363647</v>
+        <v>-35531420.80224369</v>
       </c>
       <c r="E41">
-        <v>-6881443</v>
+        <v>-24840212.949554827</v>
       </c>
       <c r="F41">
-        <v>-45283878.99972395</v>
+        <v>-11714803</v>
       </c>
       <c r="G41">
-        <v>-51406558.332642354</v>
+        <v>-7364038</v>
       </c>
       <c r="H41">
-        <v>-73049173.69318904</v>
+        <v>-48459819.23515099</v>
       </c>
       <c r="I41">
-        <v>-12469453.900909355</v>
+        <v>-55011906.65040597</v>
+      </c>
+      <c r="J41">
+        <v>-78172405.51478966</v>
+      </c>
+      <c r="K41">
+        <v>-13343986.76409323</v>
       </c>
     </row>
     <row r="42">
@@ -2244,28 +2460,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-40183443</v>
+        <v>-49184889</v>
       </c>
       <c r="C42">
-        <v>-4419497.3975019</v>
+        <v>-43001508</v>
       </c>
       <c r="D42">
-        <v>-78461270.71954313</v>
+        <v>-4729454.492943678</v>
       </c>
       <c r="E42">
-        <v>-56656982</v>
+        <v>-83964074.63354638</v>
       </c>
       <c r="F42">
-        <v>29014343.79029389</v>
+        <v>-87910439</v>
       </c>
       <c r="G42">
-        <v>226497543.6020218</v>
+        <v>-60630336</v>
       </c>
       <c r="H42">
-        <v>-103892950.68010405</v>
+        <v>31049236.204185132</v>
       </c>
       <c r="I42">
-        <v>-213733475.3068347</v>
+        <v>242382725.6544568</v>
+      </c>
+      <c r="J42">
+        <v>-111179380.4102999</v>
+      </c>
+      <c r="K42">
+        <v>-228723462.00582677</v>
       </c>
     </row>
     <row r="43">
@@ -2273,28 +2495,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>29754818</v>
+        <v>139721727</v>
       </c>
       <c r="C43">
-        <v>179144787.6003893</v>
+        <v>31841521</v>
       </c>
       <c r="D43">
-        <v>134422072.3052726</v>
+        <v>191708930.76733348</v>
       </c>
       <c r="E43">
-        <v>39999665</v>
+        <v>143849631.9002976</v>
       </c>
       <c r="F43">
-        <v>183532916.36716783</v>
+        <v>93599016</v>
       </c>
       <c r="G43">
-        <v>98673494.75492543</v>
+        <v>42804842</v>
       </c>
       <c r="H43">
-        <v>339288753.8874561</v>
+        <v>196404816.62154552</v>
       </c>
       <c r="I43">
-        <v>340837304.469307</v>
+        <v>105593863.08654025</v>
+      </c>
+      <c r="J43">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K43">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="44">
@@ -2308,28 +2536,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>29754818</v>
+        <v>139721727</v>
       </c>
       <c r="C46">
-        <v>179144787.6003893</v>
+        <v>31841521</v>
       </c>
       <c r="D46">
-        <v>134422072.3052726</v>
+        <v>191708930.76733348</v>
       </c>
       <c r="E46">
-        <v>39999665</v>
+        <v>143849631.9002976</v>
       </c>
       <c r="F46">
-        <v>183532916.36716783</v>
+        <v>93599016</v>
       </c>
       <c r="G46">
-        <v>98673494.75492543</v>
+        <v>42804842</v>
       </c>
       <c r="H46">
-        <v>339288753.8874561</v>
+        <v>196404816.62154552</v>
       </c>
       <c r="I46">
-        <v>340837304.469307</v>
+        <v>105593863.08654025</v>
+      </c>
+      <c r="J46">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K46">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="47">
@@ -2342,10 +2576,16 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
         <v>0</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2354,28 +2594,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>29754818</v>
+        <v>139721727</v>
       </c>
       <c r="C48">
-        <v>179144787.6003893</v>
+        <v>31841521</v>
       </c>
       <c r="D48">
-        <v>134422072.3052726</v>
+        <v>191708930.76733348</v>
       </c>
       <c r="E48">
-        <v>39999665</v>
+        <v>143849631.9002976</v>
       </c>
       <c r="F48">
-        <v>183532916.36716783</v>
+        <v>93599016</v>
       </c>
       <c r="G48">
-        <v>98673494.75492543</v>
+        <v>42804842</v>
       </c>
       <c r="H48">
-        <v>339288753.8874561</v>
+        <v>196404816.62154552</v>
       </c>
       <c r="I48">
-        <v>340837304.469307</v>
+        <v>105593863.08654025</v>
+      </c>
+      <c r="J48">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K48">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="49"/>
@@ -2384,40 +2630,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>30971176</v>
+        <v>65960125</v>
       </c>
       <c r="C50">
-        <v>122722629.26748002</v>
+        <v>33143308.912851658</v>
       </c>
       <c r="D50">
-        <v>86110383.89637148</v>
+        <v>131329659.95251392</v>
       </c>
       <c r="E50">
-        <v>28250660</v>
+        <v>92149650.82635824</v>
       </c>
       <c r="F50">
-        <v>114910571.43074161</v>
+        <v>62097954</v>
       </c>
       <c r="G50">
-        <v>84199046.09909065</v>
+        <v>30231992.20371683</v>
       </c>
       <c r="H50">
-        <v>116360559.18594567</v>
+        <v>122969711.13661861</v>
       </c>
       <c r="I50">
-        <v>112610996.60518172</v>
+        <v>90104263.2359068</v>
+      </c>
+      <c r="J50">
+        <v>124521392.35436058</v>
+      </c>
+      <c r="K50">
+        <v>120508857.8964398</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2428,6 +2680,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2435,27 +2689,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2469,16 +2729,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>809806419</v>
+        <v>902659265</v>
       </c>
       <c r="C3">
-        <v>990506505.0796041</v>
+        <v>866598143</v>
+      </c>
+      <c r="D3">
+        <v>1059974702.8670268</v>
       </c>
       <c r="E3">
-        <v>966719615</v>
+        <v>1065468837.2720256</v>
       </c>
       <c r="F3">
-        <v>1166088861.8555913</v>
+        <v>908985493</v>
+      </c>
+      <c r="G3">
+        <v>1034515662</v>
+      </c>
+      <c r="H3">
+        <v>1247871355.2341528</v>
       </c>
     </row>
     <row r="4">
@@ -2501,16 +2770,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-561216857</v>
+        <v>-609996141</v>
       </c>
       <c r="C7">
-        <v>-698581614.9310904</v>
+        <v>-600574995</v>
+      </c>
+      <c r="D7">
+        <v>-747575948.1816225</v>
       </c>
       <c r="E7">
-        <v>-709681041</v>
+        <v>-774158275.8702435</v>
       </c>
       <c r="F7">
-        <v>-1013881801.9409232</v>
+        <v>-659316985</v>
+      </c>
+      <c r="G7">
+        <v>-759450972</v>
+      </c>
+      <c r="H7">
+        <v>-1084989403.1420279</v>
       </c>
     </row>
     <row r="8">
@@ -2518,16 +2796,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>248589562</v>
+        <v>292663124</v>
       </c>
       <c r="C8">
-        <v>291924890.1485132</v>
+        <v>266023148</v>
+      </c>
+      <c r="D8">
+        <v>312398754.6854036</v>
       </c>
       <c r="E8">
-        <v>257038574</v>
+        <v>291310561.4017825</v>
       </c>
       <c r="F8">
-        <v>152207059.9146682</v>
+        <v>249668508</v>
+      </c>
+      <c r="G8">
+        <v>275064690</v>
+      </c>
+      <c r="H8">
+        <v>162881952.09212482</v>
       </c>
     </row>
     <row r="9">
@@ -2555,16 +2842,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>248589562</v>
+        <v>292663124</v>
       </c>
       <c r="C13">
-        <v>291924890.1485132</v>
+        <v>266023148</v>
+      </c>
+      <c r="D13">
+        <v>312398754.6854036</v>
       </c>
       <c r="E13">
-        <v>257038574</v>
+        <v>291310561.4017825</v>
       </c>
       <c r="F13">
-        <v>152207059.9146682</v>
+        <v>249668508</v>
+      </c>
+      <c r="G13">
+        <v>275064690</v>
+      </c>
+      <c r="H13">
+        <v>162881952.09212482</v>
       </c>
     </row>
     <row r="14"/>
@@ -2573,16 +2869,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-43858955</v>
+        <v>-28633731</v>
       </c>
       <c r="C15">
-        <v>-38259136.63063122</v>
+        <v>-46934784</v>
+      </c>
+      <c r="D15">
+        <v>-40942403.48148255</v>
       </c>
       <c r="E15">
-        <v>-31886855</v>
+        <v>-32567584.62245415</v>
       </c>
       <c r="F15">
-        <v>-42890083.898609385</v>
+        <v>-34006156</v>
+      </c>
+      <c r="G15">
+        <v>-34123080</v>
+      </c>
+      <c r="H15">
+        <v>-45898137.673226744</v>
       </c>
     </row>
     <row r="16">
@@ -2590,16 +2895,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-64602917</v>
+        <v>-81416766</v>
       </c>
       <c r="C16">
-        <v>-74210612.99673882</v>
+        <v>-69133520</v>
+      </c>
+      <c r="D16">
+        <v>-79415301.21952742</v>
       </c>
       <c r="E16">
-        <v>-63677659</v>
+        <v>-66525157.274389565</v>
       </c>
       <c r="F16">
-        <v>-74553912.85306099</v>
+        <v>-67665828</v>
+      </c>
+      <c r="G16">
+        <v>-68143372</v>
+      </c>
+      <c r="H16">
+        <v>-79782678.07301933</v>
       </c>
     </row>
     <row r="17">
@@ -2612,16 +2926,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>20982412</v>
+        <v>34209261</v>
       </c>
       <c r="C18">
-        <v>21975202.071849227</v>
+        <v>22453908</v>
+      </c>
+      <c r="D18">
+        <v>23516411.216985673</v>
       </c>
       <c r="E18">
-        <v>49881464</v>
+        <v>69673195.32874599</v>
       </c>
       <c r="F18">
-        <v>35072776.46432051</v>
+        <v>49168661</v>
+      </c>
+      <c r="G18">
+        <v>53379650</v>
+      </c>
+      <c r="H18">
+        <v>37532571.084429204</v>
       </c>
     </row>
     <row r="19">
@@ -2629,16 +2952,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-13225414</v>
+        <v>-28189677</v>
       </c>
       <c r="C19">
-        <v>-9597007.58938945</v>
+        <v>-14152913</v>
+      </c>
+      <c r="D19">
+        <v>-10270084.260737032</v>
       </c>
       <c r="E19">
-        <v>-15276783</v>
+        <v>-9236811.56040889</v>
       </c>
       <c r="F19">
-        <v>-11633543.384297803</v>
+        <v>-13615780</v>
+      </c>
+      <c r="G19">
+        <v>-16348144</v>
+      </c>
+      <c r="H19">
+        <v>-12449450.487021983</v>
       </c>
     </row>
     <row r="20">
@@ -2651,16 +2983,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>147884688</v>
+        <v>188632211</v>
       </c>
       <c r="C21">
-        <v>191833335.00360286</v>
+        <v>158255839</v>
+      </c>
+      <c r="D21">
+        <v>205287376.94064212</v>
       </c>
       <c r="E21">
-        <v>196078741</v>
+        <v>252654203.27327597</v>
       </c>
       <c r="F21">
-        <v>58202296.243020535</v>
+        <v>183549405</v>
+      </c>
+      <c r="G21">
+        <v>209829744</v>
+      </c>
+      <c r="H21">
+        <v>62284256.94328606</v>
       </c>
     </row>
     <row r="22"/>
@@ -2679,16 +3020,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>53121037</v>
+        <v>40032485</v>
       </c>
       <c r="C25">
-        <v>8987028.628323674</v>
+        <v>56846415</v>
+      </c>
+      <c r="D25">
+        <v>9617325.026249345</v>
       </c>
       <c r="E25">
-        <v>197057</v>
+        <v>1600454.4090911793</v>
       </c>
       <c r="F25">
-        <v>1991311.4431096772</v>
+        <v>1958472</v>
+      </c>
+      <c r="G25">
+        <v>210876</v>
+      </c>
+      <c r="H25">
+        <v>2130970.109132454</v>
       </c>
     </row>
     <row r="26">
@@ -2731,16 +3081,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>201005725</v>
+        <v>228664696</v>
       </c>
       <c r="C33">
-        <v>200820363.63192654</v>
+        <v>215102254</v>
+      </c>
+      <c r="D33">
+        <v>214904701.96689153</v>
       </c>
       <c r="E33">
-        <v>196275798</v>
+        <v>254254657.6823672</v>
       </c>
       <c r="F33">
-        <v>60193607.686130166</v>
+        <v>185507877</v>
+      </c>
+      <c r="G33">
+        <v>210040620</v>
+      </c>
+      <c r="H33">
+        <v>64415227.05241847</v>
       </c>
     </row>
     <row r="34"/>
@@ -2754,16 +3113,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-81716670</v>
+        <v>-20240501</v>
       </c>
       <c r="C36">
-        <v>-87598879.7131477</v>
+        <v>-87447460</v>
+      </c>
+      <c r="D36">
+        <v>-93742540.83062875</v>
       </c>
       <c r="E36">
-        <v>-191284637</v>
+        <v>-170698794.85277176</v>
       </c>
       <c r="F36">
-        <v>-25815444.486578733</v>
+        <v>-122588972</v>
+      </c>
+      <c r="G36">
+        <v>-204699429</v>
+      </c>
+      <c r="H36">
+        <v>-27625985.24968028</v>
       </c>
     </row>
     <row r="37">
@@ -2771,16 +3139,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-21527539</v>
+        <v>-54053655</v>
       </c>
       <c r="C37">
-        <v>-132550010.1937632</v>
+        <v>-23037265</v>
+      </c>
+      <c r="D37">
+        <v>-141846274.55714077</v>
       </c>
       <c r="E37">
-        <v>98546929</v>
+        <v>-24126201.346196562</v>
       </c>
       <c r="F37">
-        <v>241841778.89150047</v>
+        <v>19506137</v>
+      </c>
+      <c r="G37">
+        <v>105458025</v>
+      </c>
+      <c r="H37">
+        <v>258803113.76728374</v>
       </c>
     </row>
     <row r="38">
@@ -2788,16 +3165,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>97761516</v>
+        <v>154370540</v>
       </c>
       <c r="C38">
-        <v>-19328526.27498424</v>
+        <v>104617529</v>
+      </c>
+      <c r="D38">
+        <v>-20684113.420877934</v>
       </c>
       <c r="E38">
-        <v>103538090</v>
+        <v>59429661.483398795</v>
       </c>
       <c r="F38">
-        <v>276219942.09105194</v>
+        <v>82425042</v>
+      </c>
+      <c r="G38">
+        <v>110799216</v>
+      </c>
+      <c r="H38">
+        <v>295592355.570022</v>
       </c>
     </row>
     <row r="39"/>
@@ -2806,16 +3192,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-68006698</v>
+        <v>-46490334</v>
       </c>
       <c r="C40">
-        <v>64051241.57010097</v>
+        <v>-72776008</v>
+      </c>
+      <c r="D40">
+        <v>68543412.28791383</v>
       </c>
       <c r="E40">
-        <v>-63538425</v>
+        <v>-9179045.583101198</v>
       </c>
       <c r="F40">
-        <v>-191360520.47880954</v>
+        <v>-31630868</v>
+      </c>
+      <c r="G40">
+        <v>-67994374</v>
+      </c>
+      <c r="H40">
+        <v>-204781402.0350167</v>
       </c>
     </row>
     <row r="41">
@@ -2823,16 +3218,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-27823255</v>
+        <v>-40306953</v>
       </c>
       <c r="C41">
-        <v>-9990531.751940247</v>
+        <v>-29774500</v>
+      </c>
+      <c r="D41">
+        <v>-10691207.85268886</v>
       </c>
       <c r="E41">
-        <v>-6881443</v>
+        <v>-13125409.949554827</v>
       </c>
       <c r="F41">
-        <v>6122679.3329184055</v>
+        <v>-4350765</v>
+      </c>
+      <c r="G41">
+        <v>-7364038</v>
+      </c>
+      <c r="H41">
+        <v>6552087.41525498</v>
       </c>
     </row>
     <row r="42">
@@ -2840,16 +3244,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-40183443</v>
+        <v>-6183381</v>
       </c>
       <c r="C42">
-        <v>74041773.32204123</v>
+        <v>-43001508</v>
+      </c>
+      <c r="D42">
+        <v>79234620.14060271</v>
       </c>
       <c r="E42">
-        <v>-56656982</v>
+        <v>3946364.366453618</v>
       </c>
       <c r="F42">
-        <v>-197483199.8117279</v>
+        <v>-27280103</v>
+      </c>
+      <c r="G42">
+        <v>-60630336</v>
+      </c>
+      <c r="H42">
+        <v>-211333489.45027167</v>
       </c>
     </row>
     <row r="43">
@@ -2857,16 +3270,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>29754818</v>
+        <v>107880206</v>
       </c>
       <c r="C43">
-        <v>44722715.29511669</v>
+        <v>31841521</v>
+      </c>
+      <c r="D43">
+        <v>47859298.867035866</v>
       </c>
       <c r="E43">
-        <v>39999665</v>
+        <v>50250615.90029761</v>
       </c>
       <c r="F43">
-        <v>84859421.6122424</v>
+        <v>50794174</v>
+      </c>
+      <c r="G43">
+        <v>42804842</v>
+      </c>
+      <c r="H43">
+        <v>90810953.53500527</v>
       </c>
     </row>
     <row r="44">
@@ -2880,16 +3302,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>29754818</v>
+        <v>107880206</v>
       </c>
       <c r="C46">
-        <v>44722715.29511669</v>
+        <v>31841521</v>
+      </c>
+      <c r="D46">
+        <v>47859298.867035866</v>
       </c>
       <c r="E46">
-        <v>39999665</v>
+        <v>50250615.90029761</v>
       </c>
       <c r="F46">
-        <v>84859421.6122424</v>
+        <v>50794174</v>
+      </c>
+      <c r="G46">
+        <v>42804842</v>
+      </c>
+      <c r="H46">
+        <v>90810953.53500527</v>
       </c>
     </row>
     <row r="47">
@@ -2899,7 +3330,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2908,16 +3345,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>29754818</v>
+        <v>107880206</v>
       </c>
       <c r="C48">
-        <v>44722715.29511669</v>
+        <v>31841521</v>
+      </c>
+      <c r="D48">
+        <v>47859298.867035866</v>
       </c>
       <c r="E48">
-        <v>39999665</v>
+        <v>50250615.90029761</v>
       </c>
       <c r="F48">
-        <v>84859421.6122424</v>
+        <v>50794174</v>
+      </c>
+      <c r="G48">
+        <v>42804842</v>
+      </c>
+      <c r="H48">
+        <v>90810953.53500527</v>
       </c>
     </row>
     <row r="49"/>
@@ -2926,28 +3372,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>30971176</v>
+        <v>32816816.087148342</v>
       </c>
       <c r="C50">
-        <v>36612245.37110853</v>
+        <v>33143308.912851658</v>
+      </c>
+      <c r="D50">
+        <v>39180009.126155674</v>
       </c>
       <c r="E50">
-        <v>28250660</v>
+        <v>30051696.826358244</v>
       </c>
       <c r="F50">
-        <v>30711525.331650957</v>
+        <v>31865961.79628317</v>
+      </c>
+      <c r="G50">
+        <v>30231992.20371683</v>
+      </c>
+      <c r="H50">
+        <v>32865447.90071182</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2958,6 +3413,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2965,27 +3422,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2999,22 +3462,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>3645362630.4354343</v>
+        <v>3894700948.1390524</v>
       </c>
       <c r="C3">
-        <v>3802275826.4354343</v>
+        <v>3901027176.1390524</v>
       </c>
       <c r="D3">
-        <v>3977858183.2114215</v>
-      </c>
-      <c r="F3">
-        <v>4064186427.0770974</v>
+        <v>4068944695.1390524</v>
+      </c>
+      <c r="E3">
+        <v>4256841347.5061784</v>
       </c>
       <c r="H3">
-        <v>4012712256.490779</v>
-      </c>
-      <c r="I3">
-        <v>4518659110.91694</v>
+        <v>4349224137.696131</v>
+      </c>
+      <c r="J3">
+        <v>4294139876.8732553</v>
+      </c>
+      <c r="K3">
+        <v>4835570815.425018</v>
       </c>
     </row>
     <row r="4">
@@ -3037,22 +3503,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-2599324542.140967</v>
+        <v>-2732305360.051866</v>
       </c>
       <c r="C7">
-        <v>-2747788726.140967</v>
+        <v>-2781626204.051866</v>
       </c>
       <c r="D7">
-        <v>-3063088913.1507998</v>
-      </c>
-      <c r="F7">
-        <v>-3003524301.8925686</v>
+        <v>-2940502181.051866</v>
+      </c>
+      <c r="E7">
+        <v>-3277915636.0122714</v>
       </c>
       <c r="H7">
-        <v>-2757778661.0180564</v>
-      </c>
-      <c r="I7">
-        <v>-3249249911.5504003</v>
+        <v>-3214173519.432472</v>
+      </c>
+      <c r="J7">
+        <v>-2951192750.1684747</v>
+      </c>
+      <c r="K7">
+        <v>-3477132852.610144</v>
       </c>
     </row>
     <row r="8">
@@ -3060,22 +3529,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1046038088.2944673</v>
+        <v>1162395588.087186</v>
       </c>
       <c r="C8">
-        <v>1054487100.2944673</v>
+        <v>1119400972.087186</v>
       </c>
       <c r="D8">
-        <v>914769270.0606223</v>
-      </c>
-      <c r="F8">
-        <v>1060662125.1845287</v>
+        <v>1128442514.087186</v>
+      </c>
+      <c r="E8">
+        <v>978925711.4939073</v>
       </c>
       <c r="H8">
-        <v>1254933595.4727223</v>
-      </c>
-      <c r="I8">
-        <v>1269409199.3665397</v>
+        <v>1135050618.263658</v>
+      </c>
+      <c r="J8">
+        <v>1342947126.7047803</v>
+      </c>
+      <c r="K8">
+        <v>1358437962.8148742</v>
       </c>
     </row>
     <row r="9">
@@ -3103,22 +3575,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1046038088.2944673</v>
+        <v>1162395588.087186</v>
       </c>
       <c r="C13">
-        <v>1054487100.2944673</v>
+        <v>1119400972.087186</v>
       </c>
       <c r="D13">
-        <v>914769270.0606223</v>
-      </c>
-      <c r="F13">
-        <v>1060662125.1845287</v>
+        <v>1128442514.087186</v>
+      </c>
+      <c r="E13">
+        <v>978925711.4939073</v>
       </c>
       <c r="H13">
-        <v>1254933595.4727223</v>
-      </c>
-      <c r="I13">
-        <v>1269409199.3665397</v>
+        <v>1135050618.263658</v>
+      </c>
+      <c r="J13">
+        <v>1342947126.7047803</v>
+      </c>
+      <c r="K13">
+        <v>1358437962.8148742</v>
       </c>
     </row>
     <row r="14"/>
@@ -3127,22 +3602,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-144328629.33028257</v>
+        <v>-149078503.1039367</v>
       </c>
       <c r="C15">
-        <v>-132356529.33028257</v>
+        <v>-154450928.1039367</v>
       </c>
       <c r="D15">
-        <v>-136987476.59826073</v>
-      </c>
-      <c r="F15">
-        <v>-130686036.95100275</v>
+        <v>-141639224.1039367</v>
+      </c>
+      <c r="E15">
+        <v>-146594958.29568088</v>
       </c>
       <c r="H15">
-        <v>-92019073.63491544</v>
-      </c>
-      <c r="I15">
-        <v>-50948886.57566776</v>
+        <v>-139851573.3875727</v>
+      </c>
+      <c r="J15">
+        <v>-98472740.69788134</v>
+      </c>
+      <c r="K15">
+        <v>-54522136.53570008</v>
       </c>
     </row>
     <row r="16">
@@ -3150,22 +3628,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-264209720.15493459</v>
+        <v>-296490744.493917</v>
       </c>
       <c r="C16">
-        <v>-263284462.15493459</v>
+        <v>-282739806.493917</v>
       </c>
       <c r="D16">
-        <v>-263627762.01125675</v>
-      </c>
-      <c r="F16">
-        <v>-265063845.69693813</v>
+        <v>-281749658.493917</v>
+      </c>
+      <c r="E16">
+        <v>-282117035.3474089</v>
       </c>
       <c r="H16">
-        <v>-196074806.07422146</v>
-      </c>
-      <c r="I16">
-        <v>-183281415.86387584</v>
+        <v>-283653837.3474119</v>
+      </c>
+      <c r="J16">
+        <v>-209826319.40567592</v>
+      </c>
+      <c r="K16">
+        <v>-196135677.37825865</v>
       </c>
     </row>
     <row r="17">
@@ -3178,22 +3659,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>154010672.2560368</v>
+        <v>149852775.54573166</v>
       </c>
       <c r="C18">
-        <v>182909724.2560368</v>
+        <v>164812175.54573166</v>
       </c>
       <c r="D18">
-        <v>196007298.64850807</v>
-      </c>
-      <c r="F18">
-        <v>156119464.3624323</v>
+        <v>195737917.54573166</v>
+      </c>
+      <c r="E18">
+        <v>209754077.4131752</v>
       </c>
       <c r="H18">
-        <v>322213901.2797679</v>
-      </c>
-      <c r="I18">
-        <v>315769092.6944779</v>
+        <v>167068749.17093974</v>
+      </c>
+      <c r="J18">
+        <v>344812055.7685777</v>
+      </c>
+      <c r="K18">
+        <v>337915246.8832301</v>
       </c>
     </row>
     <row r="19">
@@ -3201,22 +3685,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-44177252.03399955</v>
+        <v>-61849485.82114592</v>
       </c>
       <c r="C19">
-        <v>-46228621.03399955</v>
+        <v>-47275588.82114592</v>
       </c>
       <c r="D19">
-        <v>-48265156.8289079</v>
-      </c>
-      <c r="F19">
-        <v>-99386646.98332608</v>
+        <v>-49470819.82114592</v>
+      </c>
+      <c r="E19">
+        <v>-51650186.04743087</v>
       </c>
       <c r="H19">
-        <v>-289443993.4779848</v>
-      </c>
-      <c r="I19">
-        <v>-165278392.69624794</v>
+        <v>-106357031.54381068</v>
+      </c>
+      <c r="J19">
+        <v>-309743862.7713158</v>
+      </c>
+      <c r="K19">
+        <v>-176870029.91915292</v>
       </c>
     </row>
     <row r="20">
@@ -3229,22 +3716,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>747333159.0312874</v>
+        <v>804829630.2139181</v>
       </c>
       <c r="C21">
-        <v>795527212.0312874</v>
+        <v>799746824.2139181</v>
       </c>
       <c r="D21">
-        <v>661896173.2707051</v>
-      </c>
-      <c r="F21">
-        <v>721645059.9156941</v>
+        <v>851320729.2139181</v>
+      </c>
+      <c r="E21">
+        <v>708317609.216562</v>
       </c>
       <c r="H21">
-        <v>999609623.5653684</v>
-      </c>
-      <c r="I21">
-        <v>1185669596.9252262</v>
+        <v>772256925.1558027</v>
+      </c>
+      <c r="J21">
+        <v>1069716259.5984849</v>
+      </c>
+      <c r="K21">
+        <v>1268825365.8649926</v>
       </c>
     </row>
     <row r="22"/>
@@ -3263,30 +3753,33 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>65433747.23611289</v>
+        <v>108096679.43534052</v>
       </c>
       <c r="C25">
-        <v>12509767.236112889</v>
+        <v>70022666.43534052</v>
       </c>
       <c r="D25">
-        <v>5514050.050898892</v>
-      </c>
-      <c r="F25">
-        <v>8855445.004106583</v>
+        <v>13387127.435340524</v>
+      </c>
+      <c r="E25">
+        <v>5900772.518223633</v>
       </c>
       <c r="H25">
-        <v>165081138.68157706</v>
-      </c>
-      <c r="I25">
-        <v>438544.87443053914</v>
+        <v>9476512.914197167</v>
+      </c>
+      <c r="J25">
+        <v>176658941.6885175</v>
+      </c>
+      <c r="K25">
+        <v>469301.787100338</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="I26">
-        <v>-5417.905370008493</v>
+      <c r="K26">
+        <v>-5797.884824870368</v>
       </c>
     </row>
     <row r="27">
@@ -3324,22 +3817,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>812766906.2674004</v>
+        <v>912926309.6492587</v>
       </c>
       <c r="C33">
-        <v>808036979.2674004</v>
+        <v>869769490.6492587</v>
       </c>
       <c r="D33">
-        <v>667410223.321604</v>
-      </c>
-      <c r="F33">
-        <v>730500504.9198006</v>
+        <v>864707856.6492587</v>
+      </c>
+      <c r="E33">
+        <v>714218381.7347857</v>
       </c>
       <c r="H33">
-        <v>1164690762.2469456</v>
-      </c>
-      <c r="I33">
-        <v>1186102723.8942866</v>
+        <v>781733438.0699998</v>
+      </c>
+      <c r="J33">
+        <v>1246375201.2870026</v>
+      </c>
+      <c r="K33">
+        <v>1269288869.7672682</v>
       </c>
     </row>
     <row r="34"/>
@@ -3353,22 +3849,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-443381223.059564</v>
+        <v>-372129296.6834005</v>
       </c>
       <c r="C36">
-        <v>-552949190.059564</v>
+        <v>-474477767.6834005</v>
       </c>
       <c r="D36">
-        <v>-491165754.83299506</v>
-      </c>
-      <c r="F36">
-        <v>-260230800.89275357</v>
+        <v>-591729736.6834005</v>
+      </c>
+      <c r="E36">
+        <v>-525613181.10245204</v>
       </c>
       <c r="H36">
-        <v>-179406726.9997446</v>
-      </c>
-      <c r="I36">
-        <v>-278392905.4030803</v>
+        <v>-278481831.7078862</v>
+      </c>
+      <c r="J36">
+        <v>-191989241.02837357</v>
+      </c>
+      <c r="K36">
+        <v>-297917717.52291805</v>
       </c>
     </row>
     <row r="37">
@@ -3376,22 +3875,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-158395195.44164127</v>
+        <v>-243063395.90333736</v>
       </c>
       <c r="C37">
-        <v>-38320727.44164126</v>
+        <v>-169503603.90333736</v>
       </c>
       <c r="D37">
-        <v>336071061.6436224</v>
-      </c>
-      <c r="F37">
-        <v>-270467252.4504492</v>
+        <v>-41008313.903337345</v>
+      </c>
+      <c r="E37">
+        <v>359641074.42108715</v>
       </c>
       <c r="H37">
-        <v>-469053156.98645175</v>
-      </c>
-      <c r="I37">
-        <v>-340669584.8141553</v>
+        <v>-289436206.7096023</v>
+      </c>
+      <c r="J37">
+        <v>-501949737.9934903</v>
+      </c>
+      <c r="K37">
+        <v>-364562110.4832592</v>
       </c>
     </row>
     <row r="38">
@@ -3399,22 +3901,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>210990487.76619512</v>
+        <v>297733617.06252086</v>
       </c>
       <c r="C38">
-        <v>216767061.76619512</v>
+        <v>225788119.06252086</v>
       </c>
       <c r="D38">
-        <v>512315530.1322313</v>
-      </c>
-      <c r="F38">
-        <v>199802451.57659787</v>
+        <v>231969806.06252086</v>
+      </c>
+      <c r="E38">
+        <v>548246275.0534208</v>
       </c>
       <c r="H38">
-        <v>516230878.2607492</v>
-      </c>
-      <c r="I38">
-        <v>567040233.6770511</v>
+        <v>213815399.65251136</v>
+      </c>
+      <c r="J38">
+        <v>552436222.2651386</v>
+      </c>
+      <c r="K38">
+        <v>606809041.7610908</v>
       </c>
     </row>
     <row r="39"/>
@@ -3423,22 +3928,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-42090547.165805794</v>
+        <v>-59901975.29518736</v>
       </c>
       <c r="C40">
-        <v>-37622274.165805794</v>
+        <v>-45042509.29518736</v>
       </c>
       <c r="D40">
-        <v>-293034036.2147163</v>
-      </c>
-      <c r="F40">
-        <v>-16269535.20943006</v>
+        <v>-40260875.29518736</v>
+      </c>
+      <c r="E40">
+        <v>-313585689.61811787</v>
       </c>
       <c r="H40">
-        <v>-176942124.3732931</v>
-      </c>
-      <c r="I40">
-        <v>-226202929.20774406</v>
+        <v>-17410583.03096586</v>
+      </c>
+      <c r="J40">
+        <v>-189351785.92508957</v>
+      </c>
+      <c r="K40">
+        <v>-242067448.76992002</v>
       </c>
     </row>
     <row r="41">
@@ -3446,22 +3954,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-54144588.76830389</v>
+        <v>-93898070.80224368</v>
       </c>
       <c r="C41">
-        <v>-33202776.768303894</v>
+        <v>-57941882.80224369</v>
       </c>
       <c r="D41">
-        <v>-17089565.68344524</v>
-      </c>
-      <c r="F41">
-        <v>-45283878.99972395</v>
+        <v>-35531420.80224369</v>
+      </c>
+      <c r="E41">
+        <v>-18288125.534299847</v>
       </c>
       <c r="H41">
-        <v>-73049173.69318904</v>
-      </c>
-      <c r="I41">
-        <v>-12469453.900909355</v>
+        <v>-48459819.23515099</v>
+      </c>
+      <c r="J41">
+        <v>-78172405.51478966</v>
+      </c>
+      <c r="K41">
+        <v>-13343986.76409323</v>
       </c>
     </row>
     <row r="42">
@@ -3469,22 +3980,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>12054041.6024981</v>
+        <v>33996095.507056326</v>
       </c>
       <c r="C42">
-        <v>-4419497.3975019</v>
+        <v>12899373.507056326</v>
       </c>
       <c r="D42">
-        <v>-275944470.53127104</v>
-      </c>
-      <c r="F42">
-        <v>29014343.79029389</v>
+        <v>-4729454.492943678</v>
+      </c>
+      <c r="E42">
+        <v>-295297564.0838181</v>
       </c>
       <c r="H42">
-        <v>-103892950.68010405</v>
-      </c>
-      <c r="I42">
-        <v>-213733475.3068347</v>
+        <v>31049236.204185132</v>
+      </c>
+      <c r="J42">
+        <v>-111179380.4102999</v>
+      </c>
+      <c r="K42">
+        <v>-228723462.00582677</v>
       </c>
     </row>
     <row r="43">
@@ -3492,22 +4006,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>168899940.6003893</v>
+        <v>237831641.76733348</v>
       </c>
       <c r="C43">
-        <v>179144787.6003893</v>
+        <v>180745609.76733348</v>
       </c>
       <c r="D43">
-        <v>219281493.917515</v>
-      </c>
-      <c r="F43">
-        <v>183532916.36716783</v>
+        <v>191708930.76733348</v>
+      </c>
+      <c r="E43">
+        <v>234660585.43530288</v>
       </c>
       <c r="H43">
-        <v>339288753.8874561</v>
-      </c>
-      <c r="I43">
-        <v>340837304.469307</v>
+        <v>196404816.62154552</v>
+      </c>
+      <c r="J43">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K43">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="44">
@@ -3521,22 +4038,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>168899940.6003893</v>
+        <v>237831641.76733348</v>
       </c>
       <c r="C46">
-        <v>179144787.6003893</v>
+        <v>180745609.76733348</v>
       </c>
       <c r="D46">
-        <v>219281493.917515</v>
-      </c>
-      <c r="F46">
-        <v>183532916.36716783</v>
+        <v>191708930.76733348</v>
+      </c>
+      <c r="E46">
+        <v>234660585.43530288</v>
       </c>
       <c r="H46">
-        <v>339288753.8874561</v>
-      </c>
-      <c r="I46">
-        <v>340837304.469307</v>
+        <v>196404816.62154552</v>
+      </c>
+      <c r="J46">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K46">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="47">
@@ -3549,7 +4069,10 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -3558,22 +4081,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>168899940.6003893</v>
+        <v>237831641.76733348</v>
       </c>
       <c r="C48">
-        <v>179144787.6003893</v>
+        <v>180745609.76733348</v>
       </c>
       <c r="D48">
-        <v>219281493.917515</v>
-      </c>
-      <c r="F48">
-        <v>183532916.36716783</v>
+        <v>191708930.76733348</v>
+      </c>
+      <c r="E48">
+        <v>234660585.43530288</v>
       </c>
       <c r="H48">
-        <v>339288753.8874561</v>
-      </c>
-      <c r="I48">
-        <v>340837304.469307</v>
+        <v>196404816.62154552</v>
+      </c>
+      <c r="J48">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K48">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="49"/>
@@ -3582,34 +4108,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>125443145.26748002</v>
+        <v>135191830.95251393</v>
       </c>
       <c r="C50">
-        <v>122722629.26748002</v>
+        <v>134240976.66164875</v>
       </c>
       <c r="D50">
-        <v>116821909.22802244</v>
-      </c>
-      <c r="F50">
-        <v>114910571.43074161</v>
+        <v>131329659.95251392</v>
+      </c>
+      <c r="E50">
+        <v>125015098.72707006</v>
       </c>
       <c r="H50">
-        <v>116360559.18594567</v>
-      </c>
-      <c r="I50">
-        <v>112610996.60518172</v>
+        <v>122969711.13661861</v>
+      </c>
+      <c r="J50">
+        <v>124521392.35436058</v>
+      </c>
+      <c r="K50">
+        <v>120508857.8964398</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3620,6 +4149,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3627,27 +4158,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3661,28 +4198,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>174297852</v>
+        <v>299594474</v>
       </c>
       <c r="C3">
-        <v>523453258.6673212</v>
+        <v>186522060.11429787</v>
       </c>
       <c r="D3">
-        <v>351638942.6726558</v>
+        <v>560165137.2053121</v>
       </c>
       <c r="E3">
-        <v>-120208024</v>
+        <v>376300793.4470543</v>
       </c>
       <c r="F3">
-        <v>200346.13819520926</v>
+        <v>-129959610</v>
       </c>
       <c r="G3">
-        <v>-3928015.8436930166</v>
+        <v>-128638695.32224046</v>
       </c>
       <c r="H3">
-        <v>-8487238.333254138</v>
+        <v>214397.21719642446</v>
       </c>
       <c r="I3">
-        <v>1191126846.9908233</v>
+        <v>-4203503.364615321</v>
+      </c>
+      <c r="J3">
+        <v>-9082482.431278622</v>
+      </c>
+      <c r="K3">
+        <v>1274665354.7869105</v>
       </c>
     </row>
     <row r="4">
@@ -3690,28 +4233,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>29754818</v>
+        <v>139721727</v>
       </c>
       <c r="C4">
-        <v>179144787.6003893</v>
+        <v>31841642.842999533</v>
       </c>
       <c r="D4">
-        <v>134422072.3052726</v>
+        <v>191708930.76733348</v>
       </c>
       <c r="E4">
-        <v>39999665</v>
+        <v>143849631.9002976</v>
       </c>
       <c r="F4">
-        <v>183532916.36716783</v>
+        <v>93599016</v>
       </c>
       <c r="G4">
-        <v>98673494.75492543</v>
+        <v>42805002.09309393</v>
       </c>
       <c r="H4">
-        <v>339288753.8874561</v>
+        <v>196404816.62154552</v>
       </c>
       <c r="I4">
-        <v>340837304.469307</v>
+        <v>105593863.08654025</v>
+      </c>
+      <c r="J4">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K4">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="5">
@@ -3719,28 +4268,34 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-226234631</v>
+        <v>-194152391</v>
       </c>
       <c r="C5">
-        <v>711041141.124316</v>
+        <v>-242101373.93614003</v>
       </c>
       <c r="D5">
-        <v>678696379.0072938</v>
+        <v>760909310.9680355</v>
       </c>
       <c r="E5">
-        <v>358897369</v>
+        <v>726296080.829239</v>
       </c>
       <c r="F5">
-        <v>220966430.73845646</v>
+        <v>547697644</v>
       </c>
       <c r="G5">
-        <v>15928649.826260237</v>
+        <v>384068282.3531373</v>
       </c>
       <c r="H5">
-        <v>292560894.4560973</v>
+        <v>236463693.64001232</v>
       </c>
       <c r="I5">
-        <v>1029399693.7487779</v>
+        <v>17045789.987321887</v>
+      </c>
+      <c r="J5">
+        <v>313079364.5284449</v>
+      </c>
+      <c r="K5">
+        <v>1101595627.0020432</v>
       </c>
     </row>
     <row r="6">
@@ -3748,28 +4303,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>30971176</v>
+        <v>65960125</v>
       </c>
       <c r="C6">
-        <v>122722629.26748002</v>
+        <v>33143308.912851658</v>
       </c>
       <c r="D6">
-        <v>86110383.89637148</v>
+        <v>131329659.95251392</v>
       </c>
       <c r="E6">
-        <v>28250660</v>
+        <v>92149650.82635824</v>
       </c>
       <c r="F6">
-        <v>114910571.43074161</v>
+        <v>62097954</v>
       </c>
       <c r="G6">
-        <v>84199046.09909065</v>
+        <v>30231992.20371683</v>
       </c>
       <c r="H6">
-        <v>116360559.18594567</v>
+        <v>122969711.13661861</v>
       </c>
       <c r="I6">
-        <v>112610996.60518172</v>
+        <v>90104263.2359068</v>
+      </c>
+      <c r="J6">
+        <v>124521392.35436058</v>
+      </c>
+      <c r="K6">
+        <v>120508857.8964398</v>
       </c>
     </row>
     <row r="7">
@@ -3782,28 +4343,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>874382</v>
+        <v>3614414</v>
       </c>
       <c r="C8">
-        <v>4516318.030849177</v>
+        <v>935705.9200411717</v>
       </c>
       <c r="D8">
-        <v>3723458.3364080754</v>
+        <v>4833065.54601337</v>
       </c>
       <c r="E8">
-        <v>3671722</v>
+        <v>3984599.4181075194</v>
       </c>
       <c r="F8">
-        <v>13249807.661751857</v>
+        <v>4206886</v>
       </c>
       <c r="G8">
-        <v>5494586.300716911</v>
+        <v>3929234.6047212905</v>
       </c>
       <c r="H8">
-        <v>10357124.216558466</v>
+        <v>14179069.867069643</v>
       </c>
       <c r="I8">
-        <v>3833335.708073722</v>
+        <v>5879943.697100279</v>
+      </c>
+      <c r="J8">
+        <v>11083510.918609418</v>
+      </c>
+      <c r="K8">
+        <v>4102182.930972731</v>
       </c>
     </row>
     <row r="9">
@@ -3826,28 +4393,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>19018439</v>
+        <v>-12488031</v>
       </c>
       <c r="C12">
-        <v>517570499.2690282</v>
+        <v>20352278.480391756</v>
       </c>
       <c r="D12">
-        <v>439451823.5213737</v>
+        <v>553869796.2729043</v>
       </c>
       <c r="E12">
-        <v>182492291</v>
+        <v>470272344.17204106</v>
       </c>
       <c r="F12">
-        <v>231821912.61112106</v>
+        <v>307653800</v>
       </c>
       <c r="G12">
-        <v>210691538.47932714</v>
+        <v>195291208.01957983</v>
       </c>
       <c r="H12">
-        <v>121232321.78043015</v>
+        <v>248080514.03790694</v>
       </c>
       <c r="I12">
-        <v>229180525.25102606</v>
+        <v>225468181.9361432</v>
+      </c>
+      <c r="J12">
+        <v>129734831.21826018</v>
+      </c>
+      <c r="K12">
+        <v>245253875.57787138</v>
       </c>
     </row>
     <row r="13">
@@ -3879,14 +4452,14 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>-6191176.884790843</v>
-      </c>
-      <c r="F18">
-        <v>-709858.0498766317</v>
+      <c r="D18">
+        <v>-6625388.975437339</v>
       </c>
       <c r="H18">
-        <v>-160389549.57516885</v>
+        <v>-759643.244781395</v>
+      </c>
+      <c r="J18">
+        <v>-171638312.60275543</v>
       </c>
     </row>
     <row r="19">
@@ -3899,56 +4472,68 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>68006698</v>
+        <v>116416342</v>
       </c>
       <c r="C20">
-        <v>37622274.165805794</v>
+        <v>72776280.7572115</v>
       </c>
       <c r="D20">
-        <v>101673515.73590676</v>
+        <v>40260875.29518736</v>
       </c>
       <c r="E20">
-        <v>63538424</v>
+        <v>108804287.5831012</v>
       </c>
       <c r="F20">
-        <v>16269535.20943006</v>
+        <v>99625242</v>
       </c>
       <c r="G20">
-        <v>-175090985.26937947</v>
+        <v>67994628.76281312</v>
       </c>
       <c r="H20">
-        <v>195518861.0010632</v>
+        <v>17410583.03096586</v>
       </c>
       <c r="I20">
-        <v>229374775.18760282</v>
+        <v>-187370819.00405082</v>
+      </c>
+      <c r="J20">
+        <v>209231383.67258453</v>
+      </c>
+      <c r="K20">
+        <v>245461749.04235545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="D21">
-        <v>48705206.562357076</v>
-      </c>
-      <c r="G21">
-        <v>-109365535.783495</v>
-      </c>
-      <c r="H21">
-        <v>9481577.847268665</v>
+      <c r="E21">
+        <v>52121098.23535439</v>
       </c>
       <c r="I21">
-        <v>454400060.9968935</v>
+        <v>-117035779.87777753</v>
+      </c>
+      <c r="J21">
+        <v>10146558.967385558</v>
+      </c>
+      <c r="K21">
+        <v>486268961.55440396</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>-1485858.0669973562</v>
+      <c r="B22">
+        <v>-1590522</v>
       </c>
       <c r="D22">
-        <v>-968009.0451232768</v>
+        <v>-1590067.2585098485</v>
+      </c>
+      <c r="E22">
+        <v>-1035899.4057234159</v>
+      </c>
+      <c r="F22">
+        <v>-857193</v>
       </c>
     </row>
     <row r="23">
@@ -3981,28 +4566,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>372902807</v>
+        <v>361056025</v>
       </c>
       <c r="C28">
-        <v>-355830582.0099833</v>
+        <v>399055977.9477053</v>
       </c>
       <c r="D28">
-        <v>-452447837.4211486</v>
+        <v>-380786409.27928185</v>
       </c>
       <c r="E28">
-        <v>-515894255</v>
+        <v>-484179820.70170057</v>
       </c>
       <c r="F28">
-        <v>-395061738.1257929</v>
+        <v>-764830518</v>
       </c>
       <c r="G28">
-        <v>7013348.738163826</v>
+        <v>-552075990.2636718</v>
       </c>
       <c r="H28">
-        <v>-13149448.107109128</v>
+        <v>-422769003.87480474</v>
       </c>
       <c r="I28">
-        <v>-177332901.42032298</v>
+        <v>7505223.04166048</v>
+      </c>
+      <c r="J28">
+        <v>-14071671.693946343</v>
+      </c>
+      <c r="K28">
+        <v>-189769969.73528016</v>
       </c>
     </row>
     <row r="29">
@@ -4020,28 +4611,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>693814164</v>
+        <v>742750249</v>
       </c>
       <c r="C31">
-        <v>-818870122.5726165</v>
+        <v>742474136.7768509</v>
       </c>
       <c r="D31">
-        <v>-511895562.9405088</v>
+        <v>-876300771.786287</v>
       </c>
       <c r="E31">
-        <v>-606784055</v>
+        <v>-547796853.8765006</v>
       </c>
       <c r="F31">
-        <v>352784285.872528</v>
+        <v>-517919760</v>
       </c>
       <c r="G31">
-        <v>377694737.0824835</v>
+        <v>-649340256.8329265</v>
       </c>
       <c r="H31">
-        <v>461740239.8811898</v>
+        <v>377526464.1637426</v>
       </c>
       <c r="I31">
-        <v>63531409.10704379</v>
+        <v>404183985.3250338</v>
+      </c>
+      <c r="J31">
+        <v>494123936.65247005</v>
+      </c>
+      <c r="K31">
+        <v>67987121.88725121</v>
       </c>
     </row>
     <row r="32">
@@ -4054,28 +4651,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>2462898</v>
+        <v>-25841336</v>
       </c>
       <c r="C33">
-        <v>-6416972.4835466305</v>
+        <v>2635630.9245359143</v>
       </c>
       <c r="D33">
-        <v>-3420807.803559019</v>
+        <v>-6867020.526035397</v>
       </c>
       <c r="E33">
-        <v>-301596</v>
+        <v>-3660722.788338749</v>
       </c>
       <c r="F33">
-        <v>14641697.389334267</v>
+        <v>-1782065</v>
       </c>
       <c r="G33">
-        <v>19393105.18497158</v>
+        <v>-322748.13829737715</v>
       </c>
       <c r="H33">
-        <v>11710723.221268585</v>
+        <v>15668578.409266708</v>
       </c>
       <c r="I33">
-        <v>37037600.35951319</v>
+        <v>20753221.50908762</v>
+      </c>
+      <c r="J33">
+        <v>12532043.255813405</v>
+      </c>
+      <c r="K33">
+        <v>39635195.967569694</v>
       </c>
     </row>
     <row r="34">
@@ -4098,28 +4701,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-198329302</v>
+        <v>-560209964</v>
       </c>
       <c r="C37">
-        <v>-204968915.4560698</v>
+        <v>-212238932.18185347</v>
       </c>
       <c r="D37">
-        <v>-310803240.2151924</v>
+        <v>-219344208.38565174</v>
       </c>
       <c r="E37">
-        <v>-152100482</v>
+        <v>-332601119.2331657</v>
       </c>
       <c r="F37">
-        <v>-783406.9578840424</v>
+        <v>-375967309</v>
       </c>
       <c r="G37">
-        <v>144834828.23561868</v>
+        <v>-162767899.4404227</v>
       </c>
       <c r="H37">
-        <v>-259411503.60883456</v>
+        <v>-838350.4329841458</v>
       </c>
       <c r="I37">
-        <v>-87469739.56908073</v>
+        <v>154992676.20812717</v>
+      </c>
+      <c r="J37">
+        <v>-277605073.81621337</v>
+      </c>
+      <c r="K37">
+        <v>-93604343.56979944</v>
       </c>
     </row>
     <row r="38">
@@ -4132,28 +4741,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>153191761</v>
+        <v>122651209</v>
       </c>
       <c r="C39">
-        <v>-48327159.98078472</v>
+        <v>163935714.2178502</v>
       </c>
       <c r="D39">
-        <v>-17690542.7767951</v>
+        <v>-51716537.729272865</v>
       </c>
       <c r="E39">
-        <v>-32467504</v>
+        <v>-18931251.563948896</v>
       </c>
       <c r="F39">
-        <v>-308318853.46934295</v>
+        <v>-8149081</v>
       </c>
       <c r="G39">
-        <v>-328192431.240608</v>
+        <v>-34744580.40279926</v>
       </c>
       <c r="H39">
-        <v>22535854.325859312</v>
+        <v>-329942492.4707631</v>
       </c>
       <c r="I39">
-        <v>171403543.7163595</v>
+        <v>-351209884.03757405</v>
+      </c>
+      <c r="J39">
+        <v>24116384.26441991</v>
+      </c>
+      <c r="K39">
+        <v>183424762.37094697</v>
       </c>
     </row>
     <row r="40">
@@ -4161,28 +4776,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-227246570</v>
+        <v>201514365</v>
       </c>
       <c r="C40">
-        <v>270739485.85936874</v>
+        <v>-243184284.28084126</v>
       </c>
       <c r="D40">
-        <v>173038447.76324087</v>
+        <v>289727532.94042474</v>
       </c>
       <c r="E40">
-        <v>-18390328</v>
+        <v>185174328.802285</v>
       </c>
       <c r="F40">
-        <v>-851451.5548383975</v>
+        <v>908156</v>
       </c>
       <c r="G40">
-        <v>160823355.2178355</v>
+        <v>-19680115.534284696</v>
       </c>
       <c r="H40">
-        <v>-765953.7879021864</v>
+        <v>-911167.2707015343</v>
       </c>
       <c r="I40">
-        <v>-131292236.33646747</v>
+        <v>172102542.77674168</v>
+      </c>
+      <c r="J40">
+        <v>-819673.2021222255</v>
+      </c>
+      <c r="K40">
+        <v>-140500287.96964857</v>
       </c>
     </row>
     <row r="41">
@@ -4195,28 +4816,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>4692166</v>
+        <v>-4146777</v>
       </c>
       <c r="C42">
-        <v>-1350670.1187408755</v>
+        <v>5021246.439217533</v>
       </c>
       <c r="D42">
-        <v>2597762.751694276</v>
+        <v>-1445398.0367031225</v>
       </c>
       <c r="E42">
-        <v>2420588</v>
+        <v>2779954.282707991</v>
       </c>
       <c r="F42">
-        <v>15938067.182422798</v>
+        <v>-10377067</v>
       </c>
       <c r="G42">
-        <v>9051933.81737457</v>
+        <v>2590353.5543739693</v>
       </c>
       <c r="H42">
-        <v>24227254.79249351</v>
+        <v>17055867.820479985</v>
       </c>
       <c r="I42">
-        <v>-16020705.98693878</v>
+        <v>9686782.276783224</v>
+      </c>
+      <c r="J42">
+        <v>25926409.436244145</v>
+      </c>
+      <c r="K42">
+        <v>-17144302.416126657</v>
       </c>
     </row>
     <row r="43">
@@ -4229,28 +4856,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>140014027</v>
+        <v>139625268</v>
       </c>
       <c r="C44">
-        <v>13594.613904327707</v>
+        <v>149833772.8277852</v>
       </c>
       <c r="D44">
-        <v>-17195.36138416854</v>
+        <v>14548.058755730863</v>
       </c>
       <c r="E44">
-        <v>131020</v>
+        <v>-18401.341112252838</v>
       </c>
       <c r="F44">
-        <v>45461.73581265101</v>
+        <v>66929</v>
       </c>
       <c r="G44">
-        <v>66160.91563960775</v>
+        <v>140208.95860595748</v>
       </c>
       <c r="H44">
-        <v>18522677.002251115</v>
+        <v>48650.149860410325</v>
       </c>
       <c r="I44">
-        <v>-249719238.37321588</v>
+        <v>70801.04626962302</v>
+      </c>
+      <c r="J44">
+        <v>19821746.703405187</v>
+      </c>
+      <c r="K44">
+        <v>-267233051.10808623</v>
       </c>
     </row>
     <row r="45">
@@ -4268,28 +4901,34 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-176521295</v>
+        <v>-214455509</v>
       </c>
       <c r="C47">
-        <v>431784798.0184583</v>
+        <v>-188901442.09834385</v>
       </c>
       <c r="D47">
-        <v>215417369.02327734</v>
+        <v>462067599.3898011</v>
       </c>
       <c r="E47">
-        <v>275414166</v>
+        <v>230525453.9489312</v>
       </c>
       <c r="F47">
-        <v>-454549359.7472815</v>
+        <v>135368840</v>
       </c>
       <c r="G47">
-        <v>-337050806.42683876</v>
+        <v>294730067.1667555</v>
       </c>
       <c r="H47">
-        <v>-229007539.27242652</v>
+        <v>-486428731.22554624</v>
       </c>
       <c r="I47">
-        <v>96090205.78010346</v>
+        <v>-360689532.6393316</v>
+      </c>
+      <c r="J47">
+        <v>-245068757.3981059</v>
+      </c>
+      <c r="K47">
+        <v>102829397.68478449</v>
       </c>
     </row>
     <row r="48">
@@ -4297,28 +4936,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-19175042</v>
+        <v>-40831480</v>
       </c>
       <c r="C48">
-        <v>21565380.110043913</v>
+        <v>-20519864.677495774</v>
       </c>
       <c r="D48">
-        <v>325932.13807829603</v>
+        <v>23077846.79568681</v>
       </c>
       <c r="E48">
-        <v>16183936</v>
+        <v>348791.0674413909</v>
       </c>
       <c r="F48">
-        <v>-13968178.57654381</v>
+        <v>13020839</v>
       </c>
       <c r="G48">
-        <v>-821323.6783696937</v>
+        <v>17318980.40532335</v>
       </c>
       <c r="H48">
-        <v>19436532.257328004</v>
+        <v>-14947823.018159466</v>
       </c>
       <c r="I48">
-        <v>66789185.95990758</v>
+        <v>-878926.405301703</v>
+      </c>
+      <c r="J48">
+        <v>20799694.296375055</v>
+      </c>
+      <c r="K48">
+        <v>71473379.70980215</v>
       </c>
     </row>
     <row r="49">
@@ -4326,16 +4971,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>176422994</v>
+        <v>306625361</v>
       </c>
       <c r="C49">
-        <v>534355346.7147219</v>
-      </c>
-      <c r="E49">
-        <v>-116997221</v>
+        <v>188796246.85456485</v>
+      </c>
+      <c r="D49">
+        <v>571831832.4560869</v>
       </c>
       <c r="F49">
-        <v>9437608.979831355</v>
+        <v>-123533858</v>
+      </c>
+      <c r="G49">
+        <v>-125202705.81744055</v>
+      </c>
+      <c r="H49">
+        <v>10099506.38675307</v>
       </c>
     </row>
     <row r="50">
@@ -4403,28 +5054,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-2125142</v>
+        <v>-7030887</v>
       </c>
       <c r="C62">
-        <v>-10902088.04740073</v>
+        <v>-2274186.740266995</v>
       </c>
       <c r="D62">
-        <v>-9031671.218762064</v>
+        <v>-11666695.25077479</v>
       </c>
       <c r="E62">
-        <v>-3210803</v>
+        <v>-9665098.580781773</v>
       </c>
       <c r="F62">
-        <v>-9237262.841636145</v>
+        <v>-6425752</v>
       </c>
       <c r="G62">
-        <v>-3928015.8436930166</v>
+        <v>-3435989.5047999094</v>
       </c>
       <c r="H62">
-        <v>-8487238.333254138</v>
+        <v>-9885109.169556646</v>
       </c>
       <c r="I62">
-        <v>-1777249.8069386615</v>
+        <v>-4203503.364615321</v>
+      </c>
+      <c r="J62">
+        <v>-9082482.431278622</v>
+      </c>
+      <c r="K62">
+        <v>-1901895.4710235745</v>
       </c>
     </row>
     <row r="63">
@@ -4448,28 +5105,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-45237009</v>
+        <v>-171458929</v>
       </c>
       <c r="C67">
-        <v>-135141581.97374973</v>
+        <v>-48409662.054177426</v>
       </c>
       <c r="D67">
-        <v>-99353594.60913157</v>
+        <v>-144619603.6704403</v>
       </c>
       <c r="E67">
-        <v>-17051746</v>
+        <v>-106321661.07391857</v>
       </c>
       <c r="F67">
-        <v>-248575829.3940641</v>
+        <v>-40040140</v>
       </c>
       <c r="G67">
-        <v>-180489662.70222914</v>
+        <v>-18247653.404619914</v>
       </c>
       <c r="H67">
-        <v>-219225512.27522406</v>
+        <v>-266009450.26678282</v>
       </c>
       <c r="I67">
-        <v>-611834733.4435409</v>
+        <v>-193148127.35933504</v>
+      </c>
+      <c r="J67">
+        <v>-234600677.57568857</v>
+      </c>
+      <c r="K67">
+        <v>-654745159.6326703</v>
       </c>
     </row>
     <row r="68">
@@ -4521,20 +5184,26 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>3266272.7044540634</v>
+      <c r="B77">
+        <v>2850000</v>
       </c>
       <c r="D77">
-        <v>-97955834.73775993</v>
-      </c>
-      <c r="G77">
-        <v>-154019050.58218354</v>
-      </c>
-      <c r="H77">
-        <v>-137762792.02991784</v>
+        <v>3495349.522321543</v>
+      </c>
+      <c r="E77">
+        <v>-104825870.69118147</v>
+      </c>
+      <c r="F77">
+        <v>825694</v>
       </c>
       <c r="I77">
-        <v>-593929776.8894755</v>
+        <v>-164821024.93975154</v>
+      </c>
+      <c r="J77">
+        <v>-147424649.71121874</v>
+      </c>
+      <c r="K77">
+        <v>-635584456.5924442</v>
       </c>
     </row>
     <row r="78">
@@ -4542,19 +5211,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-36516583</v>
+        <v>-131688110</v>
       </c>
       <c r="C78">
-        <v>-117666728.0918133</v>
+        <v>-39077637.56890559</v>
       </c>
       <c r="D78">
-        <v>996995.642696349</v>
+        <v>-125919168.12947264</v>
       </c>
       <c r="E78">
-        <v>-14656991</v>
+        <v>1066918.9497567727</v>
       </c>
       <c r="F78">
-        <v>-205686691.04253715</v>
+        <v>-38303125</v>
+      </c>
+      <c r="G78">
+        <v>-15684944.622247683</v>
+      </c>
+      <c r="H78">
+        <v>-220112324.4556515</v>
       </c>
     </row>
     <row r="79">
@@ -4652,16 +5327,22 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B97">
-        <v>-8720426</v>
+        <v>-42620819</v>
       </c>
       <c r="C97">
-        <v>-20741126.586390503</v>
-      </c>
-      <c r="E97">
-        <v>-2394755</v>
+        <v>-9332024.485271832</v>
+      </c>
+      <c r="D97">
+        <v>-22195785.063289195</v>
       </c>
       <c r="F97">
-        <v>-42889138.351526946</v>
+        <v>-2562709</v>
+      </c>
+      <c r="G97">
+        <v>-2562708.782372231</v>
+      </c>
+      <c r="H97">
+        <v>-45897125.81113132</v>
       </c>
     </row>
     <row r="98">
@@ -4680,28 +5361,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>431579541</v>
+        <v>399752576</v>
       </c>
       <c r="C101">
-        <v>-381115815.5850444</v>
+        <v>461847946.872593</v>
       </c>
       <c r="D101">
-        <v>-191734589.60516387</v>
+        <v>-407844997.7975822</v>
       </c>
       <c r="E101">
-        <v>197186769</v>
+        <v>-205181706.13097748</v>
       </c>
       <c r="F101">
-        <v>239490842.95457146</v>
+        <v>156420819</v>
       </c>
       <c r="G101">
-        <v>112629536.68195128</v>
+        <v>211016268.75563657</v>
       </c>
       <c r="H101">
-        <v>375060116.9567418</v>
+        <v>256287297.25479603</v>
       </c>
       <c r="I101">
-        <v>-464020876.0264669</v>
+        <v>120528698.26322606</v>
+      </c>
+      <c r="J101">
+        <v>401364588.71266514</v>
+      </c>
+      <c r="K101">
+        <v>-496564522.9666847</v>
       </c>
     </row>
     <row r="102">
@@ -4719,7 +5406,10 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>921308776</v>
+        <v>985926495</v>
+      </c>
+      <c r="C104">
+        <v>985923859.2389663</v>
       </c>
     </row>
     <row r="105">
@@ -4746,26 +5436,32 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>136454683.68398374</v>
+      <c r="B109">
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>247717233.9162098</v>
+        <v>146024798.4753221</v>
       </c>
       <c r="E109">
-        <v>379679059</v>
+        <v>265090638.04106355</v>
       </c>
       <c r="F109">
-        <v>471312755.56569254</v>
+        <v>464074618</v>
       </c>
       <c r="G109">
-        <v>323321075.1612784</v>
+        <v>406307475.70508236</v>
       </c>
       <c r="H109">
-        <v>360719228.0512173</v>
+        <v>504367811.29270303</v>
       </c>
       <c r="I109">
-        <v>64032091.08608882</v>
+        <v>345996880.19936925</v>
+      </c>
+      <c r="J109">
+        <v>386017915.69383353</v>
+      </c>
+      <c r="K109">
+        <v>68522918.70357448</v>
       </c>
     </row>
     <row r="110">
@@ -4773,19 +5469,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-470710796</v>
-      </c>
-      <c r="D110">
-        <v>-439451823.5213737</v>
-      </c>
-      <c r="G110">
-        <v>-210691538.47932714</v>
-      </c>
-      <c r="H110">
-        <v>-253827796.32465953</v>
+        <v>-598661950</v>
+      </c>
+      <c r="C110">
+        <v>-503723633.88598156</v>
+      </c>
+      <c r="E110">
+        <v>-470272344.17204106</v>
       </c>
       <c r="I110">
-        <v>-234840350.77544087</v>
+        <v>-225468181.9361432</v>
+      </c>
+      <c r="J110">
+        <v>-271629758.7232911</v>
+      </c>
+      <c r="K110">
+        <v>-251310647.38881338</v>
       </c>
     </row>
     <row r="111">
@@ -4827,46 +5526,52 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="B118">
-        <v>-19018439</v>
-      </c>
       <c r="C118">
-        <v>-517570499.2690282</v>
+        <v>-20352278.480391756</v>
       </c>
       <c r="D118">
-        <v>-47291327.33157916</v>
+        <v>-553869796.2729043</v>
       </c>
       <c r="E118">
-        <v>-182492290</v>
+        <v>-50608057.97782147</v>
       </c>
       <c r="F118">
-        <v>-231821912.61112106</v>
+        <v>-307653799</v>
       </c>
       <c r="G118">
-        <v>-28722200.805311203</v>
+        <v>-195291206.9494458</v>
       </c>
       <c r="H118">
-        <v>-2204302.015633074</v>
+        <v>-248080514.03790694</v>
       </c>
       <c r="I118">
-        <v>-240563.95554196043</v>
+        <v>-30736604.05879925</v>
+      </c>
+      <c r="J118">
+        <v>-2358898.5656001098</v>
+      </c>
+      <c r="K118">
+        <v>-257435.6715361634</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="D119">
-        <v>11508520.975516897</v>
-      </c>
-      <c r="G119">
-        <v>1026699.9577039813</v>
-      </c>
-      <c r="H119">
-        <v>36696.60534209229</v>
+      <c r="B119">
+        <v>12488031</v>
+      </c>
+      <c r="E119">
+        <v>12315659.75478585</v>
       </c>
       <c r="I119">
-        <v>68264.68898379078</v>
+        <v>1098706.5476297957</v>
+      </c>
+      <c r="J119">
+        <v>39270.285600584466</v>
+      </c>
+      <c r="K119">
+        <v>73052.36568445187</v>
       </c>
     </row>
     <row r="120">
@@ -4888,17 +5593,17 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="D123">
-        <v>-2394755.514067985</v>
-      </c>
-      <c r="G123">
-        <v>-26470612.120045613</v>
-      </c>
-      <c r="H123">
-        <v>-81462720.24530622</v>
+      <c r="E123">
+        <v>-2562709.332493868</v>
       </c>
       <c r="I123">
-        <v>-17904956.55406537</v>
+        <v>-28327102.419583514</v>
+      </c>
+      <c r="J123">
+        <v>-87176027.86446983</v>
+      </c>
+      <c r="K123">
+        <v>-19160703.04022606</v>
       </c>
     </row>
     <row r="124">
@@ -4911,45 +5616,51 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>560640384</v>
+        <v>527888121</v>
       </c>
       <c r="C125">
-        <v>7195861.108527065</v>
+        <v>599960344.9327134</v>
       </c>
       <c r="D125">
-        <v>60550758.45836031</v>
+        <v>7700535.737289656</v>
       </c>
       <c r="E125">
-        <v>59926999</v>
+        <v>64797426.24215823</v>
       </c>
       <c r="F125">
-        <v>-8884640.30129743</v>
+        <v>-13578931</v>
       </c>
       <c r="G125">
-        <v>49827351.45537862</v>
+        <v>64129920.02877618</v>
       </c>
       <c r="H125">
-        <v>15927332.671224333</v>
+        <v>-9507755.794790361</v>
       </c>
       <c r="I125">
-        <v>115271237.52081539</v>
+        <v>53321943.65479833</v>
+      </c>
+      <c r="J125">
+        <v>17044380.454915334</v>
+      </c>
+      <c r="K125">
+        <v>123355672.18755533</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
-      <c r="B126">
-        <v>-3667870</v>
-      </c>
       <c r="C126">
-        <v>-10193549.403552208</v>
-      </c>
-      <c r="E126">
-        <v>-3948945</v>
-      </c>
-      <c r="F126">
-        <v>-23110537.720029484</v>
+        <v>-3925112.448496667</v>
+      </c>
+      <c r="D126">
+        <v>-10908463.947263274</v>
+      </c>
+      <c r="G126">
+        <v>-4225900.366678392</v>
+      </c>
+      <c r="H126">
+        <v>-24731372.512204498</v>
       </c>
     </row>
     <row r="127">
@@ -4957,28 +5668,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>556972514</v>
+        <v>527888121</v>
       </c>
       <c r="C127">
-        <v>-2997688.2950251433</v>
+        <v>596035232.4842168</v>
       </c>
       <c r="D127">
-        <v>51794069.47825803</v>
+        <v>-3207928.2099736193</v>
       </c>
       <c r="E127">
-        <v>55978054</v>
+        <v>55426595.50840457</v>
       </c>
       <c r="F127">
-        <v>-31995178.021326914</v>
+        <v>-13578931</v>
       </c>
       <c r="G127">
-        <v>29982195.67637992</v>
+        <v>59904019.6620978</v>
       </c>
       <c r="H127">
-        <v>-65789549.11705205</v>
+        <v>-34239128.306994855</v>
       </c>
       <c r="I127">
-        <v>40523553.93917237</v>
+        <v>32084967.42867707</v>
+      </c>
+      <c r="J127">
+        <v>-70403634.32191542</v>
+      </c>
+      <c r="K127">
+        <v>43365633.466827236</v>
       </c>
     </row>
     <row r="128">
@@ -4986,16 +5703,22 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>40193162</v>
+        <v>43012184</v>
       </c>
       <c r="C128">
-        <v>43190924.69480089</v>
-      </c>
-      <c r="E128">
-        <v>43191166</v>
+        <v>43012069.81453628</v>
+      </c>
+      <c r="D128">
+        <v>46220077.64224061</v>
       </c>
       <c r="F128">
-        <v>75186102.7161278</v>
+        <v>46220345</v>
+      </c>
+      <c r="G128">
+        <v>46220335.871142104</v>
+      </c>
+      <c r="H128">
+        <v>80459205.94923547</v>
       </c>
     </row>
     <row r="129">
@@ -5003,28 +5726,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>597165676</v>
+        <v>564413413</v>
       </c>
       <c r="C129">
-        <v>40193236.39977574</v>
-      </c>
-      <c r="E129">
-        <v>99169220</v>
+        <v>639047302.298753</v>
+      </c>
+      <c r="D129">
+        <v>43012149.43226699</v>
       </c>
       <c r="F129">
-        <v>43190924.69480089</v>
+        <v>26036017</v>
+      </c>
+      <c r="G129">
+        <v>106124355.5332399</v>
+      </c>
+      <c r="H129">
+        <v>46220077.64224061</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5035,6 +5764,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5042,27 +5773,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5076,16 +5813,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>174297852</v>
+        <v>113072413.88570213</v>
       </c>
       <c r="C3">
-        <v>171814315.99466538</v>
+        <v>186522060.11429787</v>
+      </c>
+      <c r="D3">
+        <v>183864343.7582578</v>
       </c>
       <c r="E3">
-        <v>-120208024</v>
+        <v>506260403.4470543</v>
       </c>
       <c r="F3">
-        <v>4128361.981888226</v>
+        <v>-1320914.677759543</v>
+      </c>
+      <c r="G3">
+        <v>-128638695.32224046</v>
+      </c>
+      <c r="H3">
+        <v>4417900.581811746</v>
       </c>
     </row>
     <row r="4">
@@ -5093,16 +5839,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>29754818</v>
+        <v>107880084.15700047</v>
       </c>
       <c r="C4">
-        <v>44722715.29511669</v>
+        <v>31841642.842999533</v>
+      </c>
+      <c r="D4">
+        <v>47859298.867035866</v>
       </c>
       <c r="E4">
-        <v>39999665</v>
+        <v>50250615.90029761</v>
       </c>
       <c r="F4">
-        <v>84859421.6122424</v>
+        <v>50794013.90690607</v>
+      </c>
+      <c r="G4">
+        <v>42805002.09309393</v>
+      </c>
+      <c r="H4">
+        <v>90810953.53500527</v>
       </c>
     </row>
     <row r="5">
@@ -5110,16 +5865,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-226234631</v>
+        <v>47948982.93614003</v>
       </c>
       <c r="C5">
-        <v>32344762.117022157</v>
+        <v>-242101373.93614003</v>
+      </c>
+      <c r="D5">
+        <v>34613230.13879645</v>
       </c>
       <c r="E5">
-        <v>358897369</v>
+        <v>178598436.829239</v>
       </c>
       <c r="F5">
-        <v>205037780.91219622</v>
+        <v>163629361.6468627</v>
+      </c>
+      <c r="G5">
+        <v>384068282.3531373</v>
+      </c>
+      <c r="H5">
+        <v>219417903.65269044</v>
       </c>
     </row>
     <row r="6">
@@ -5127,16 +5891,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>30971176</v>
+        <v>32816816.087148342</v>
       </c>
       <c r="C6">
-        <v>36612245.37110853</v>
+        <v>33143308.912851658</v>
+      </c>
+      <c r="D6">
+        <v>39180009.126155674</v>
       </c>
       <c r="E6">
-        <v>28250660</v>
+        <v>30051696.826358244</v>
       </c>
       <c r="F6">
-        <v>30711525.331650957</v>
+        <v>31865961.79628317</v>
+      </c>
+      <c r="G6">
+        <v>30231992.20371683</v>
+      </c>
+      <c r="H6">
+        <v>32865447.90071182</v>
       </c>
     </row>
     <row r="7">
@@ -5149,16 +5922,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>874382</v>
+        <v>2678708.079958828</v>
       </c>
       <c r="C8">
-        <v>792859.694441102</v>
+        <v>935705.9200411717</v>
+      </c>
+      <c r="D8">
+        <v>848466.1279058508</v>
       </c>
       <c r="E8">
-        <v>3671722</v>
+        <v>-222286.5818924806</v>
       </c>
       <c r="F8">
-        <v>7755221.361034946</v>
+        <v>277651.3952787095</v>
+      </c>
+      <c r="G8">
+        <v>3929234.6047212905</v>
+      </c>
+      <c r="H8">
+        <v>8299126.169969364</v>
       </c>
     </row>
     <row r="9">
@@ -5181,16 +5963,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>19018439</v>
+        <v>-32840309.480391756</v>
       </c>
       <c r="C12">
-        <v>78118675.7476545</v>
+        <v>20352278.480391756</v>
+      </c>
+      <c r="D12">
+        <v>83597452.10086322</v>
       </c>
       <c r="E12">
-        <v>182492291</v>
+        <v>162618544.17204106</v>
       </c>
       <c r="F12">
-        <v>21130374.131793916</v>
+        <v>112362591.98042017</v>
+      </c>
+      <c r="G12">
+        <v>195291208.01957983</v>
+      </c>
+      <c r="H12">
+        <v>22612332.101763755</v>
       </c>
     </row>
     <row r="13">
@@ -5233,16 +6024,25 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>68006698</v>
+        <v>43640061.24278849</v>
       </c>
       <c r="C20">
-        <v>-64051241.57010097</v>
+        <v>72776280.7572115</v>
+      </c>
+      <c r="D20">
+        <v>-68543412.28791383</v>
       </c>
       <c r="E20">
-        <v>63538424</v>
+        <v>9179045.583101198</v>
       </c>
       <c r="F20">
-        <v>191360520.47880954</v>
+        <v>31630613.23718688</v>
+      </c>
+      <c r="G20">
+        <v>67994628.76281312</v>
+      </c>
+      <c r="H20">
+        <v>204781402.0350167</v>
       </c>
     </row>
     <row r="21">
@@ -5254,8 +6054,11 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>-517849.0218740795</v>
+      <c r="D22">
+        <v>-554167.8527864326</v>
+      </c>
+      <c r="E22">
+        <v>-178706.4057234159</v>
       </c>
     </row>
     <row r="23">
@@ -5288,16 +6091,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>372902807</v>
+        <v>-37999952.94770533</v>
       </c>
       <c r="C28">
-        <v>96617255.4111653</v>
+        <v>399055977.9477053</v>
+      </c>
+      <c r="D28">
+        <v>103393411.42241871</v>
       </c>
       <c r="E28">
-        <v>-515894255</v>
+        <v>280650697.29829943</v>
       </c>
       <c r="F28">
-        <v>-402075086.86395675</v>
+        <v>-212754527.73632824</v>
+      </c>
+      <c r="G28">
+        <v>-552075990.2636718</v>
+      </c>
+      <c r="H28">
+        <v>-430274226.9164652</v>
       </c>
     </row>
     <row r="29">
@@ -5315,16 +6127,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>693814164</v>
+        <v>276112.2231490612</v>
       </c>
       <c r="C31">
-        <v>-306974559.6321077</v>
+        <v>742474136.7768509</v>
+      </c>
+      <c r="D31">
+        <v>-328503917.90978634</v>
       </c>
       <c r="E31">
-        <v>-606784055</v>
+        <v>-29877093.876500607</v>
       </c>
       <c r="F31">
-        <v>-24910451.209955454</v>
+        <v>131420496.83292651</v>
+      </c>
+      <c r="G31">
+        <v>-649340256.8329265</v>
+      </c>
+      <c r="H31">
+        <v>-26657521.161291182</v>
       </c>
     </row>
     <row r="32">
@@ -5337,16 +6158,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>2462898</v>
+        <v>-28476966.924535915</v>
       </c>
       <c r="C33">
-        <v>-2996164.6799876112</v>
+        <v>2635630.9245359143</v>
+      </c>
+      <c r="D33">
+        <v>-3206297.737696648</v>
       </c>
       <c r="E33">
-        <v>-301596</v>
+        <v>-1878657.7883387492</v>
       </c>
       <c r="F33">
-        <v>-4751407.795637311</v>
+        <v>-1459316.8617026228</v>
+      </c>
+      <c r="G33">
+        <v>-322748.13829737715</v>
+      </c>
+      <c r="H33">
+        <v>-5084643.09982091</v>
       </c>
     </row>
     <row r="34">
@@ -5369,16 +6199,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-198329302</v>
+        <v>-347971031.8181465</v>
       </c>
       <c r="C37">
-        <v>105834324.75912258</v>
+        <v>-212238932.18185347</v>
+      </c>
+      <c r="D37">
+        <v>113256910.84751394</v>
       </c>
       <c r="E37">
-        <v>-152100482</v>
+        <v>43366189.76683432</v>
       </c>
       <c r="F37">
-        <v>-145618235.19350272</v>
+        <v>-213199409.5595773</v>
+      </c>
+      <c r="G37">
+        <v>-162767899.4404227</v>
+      </c>
+      <c r="H37">
+        <v>-155831026.6411113</v>
       </c>
     </row>
     <row r="38">
@@ -5391,16 +6230,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>153191761</v>
+        <v>-41284505.21785021</v>
       </c>
       <c r="C39">
-        <v>-30636617.20398962</v>
+        <v>163935714.2178502</v>
+      </c>
+      <c r="D39">
+        <v>-32785286.16532397</v>
       </c>
       <c r="E39">
-        <v>-32467504</v>
+        <v>-10782170.563948896</v>
       </c>
       <c r="F39">
-        <v>19873577.77126503</v>
+        <v>26595499.402799264</v>
+      </c>
+      <c r="G39">
+        <v>-34744580.40279926</v>
+      </c>
+      <c r="H39">
+        <v>21267391.566810966</v>
       </c>
     </row>
     <row r="40">
@@ -5408,16 +6256,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-227246570</v>
+        <v>444698649.28084123</v>
       </c>
       <c r="C40">
-        <v>97701038.09612787</v>
+        <v>-243184284.28084126</v>
+      </c>
+      <c r="D40">
+        <v>104553204.13813975</v>
       </c>
       <c r="E40">
-        <v>-18390328</v>
+        <v>184266172.802285</v>
       </c>
       <c r="F40">
-        <v>-161674806.77267388</v>
+        <v>20588271.534284696</v>
+      </c>
+      <c r="G40">
+        <v>-19680115.534284696</v>
+      </c>
+      <c r="H40">
+        <v>-173013710.0474432</v>
       </c>
     </row>
     <row r="41">
@@ -5430,16 +6287,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>4692166</v>
+        <v>-9168023.439217534</v>
       </c>
       <c r="C42">
-        <v>-3948432.8704351513</v>
+        <v>5021246.439217533</v>
+      </c>
+      <c r="D42">
+        <v>-4225352.319411114</v>
       </c>
       <c r="E42">
-        <v>2420588</v>
+        <v>13157021.282707991</v>
       </c>
       <c r="F42">
-        <v>6886133.365048228</v>
+        <v>-12967420.554373968</v>
+      </c>
+      <c r="G42">
+        <v>2590353.5543739693</v>
+      </c>
+      <c r="H42">
+        <v>7369085.543696761</v>
       </c>
     </row>
     <row r="43">
@@ -5452,16 +6318,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>140014027</v>
+        <v>-10208504.827785194</v>
       </c>
       <c r="C44">
-        <v>30789.975288496247</v>
+        <v>149833772.8277852</v>
+      </c>
+      <c r="D44">
+        <v>32949.3998679837</v>
       </c>
       <c r="E44">
-        <v>131020</v>
+        <v>-85330.34111225283</v>
       </c>
       <c r="F44">
-        <v>-20699.179826956737</v>
+        <v>-73279.95860595748</v>
+      </c>
+      <c r="G44">
+        <v>140208.95860595748</v>
+      </c>
+      <c r="H44">
+        <v>-22150.8964092127</v>
       </c>
     </row>
     <row r="45">
@@ -5479,16 +6354,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-176521295</v>
+        <v>-25554066.90165615</v>
       </c>
       <c r="C47">
-        <v>216367428.99518096</v>
+        <v>-188901442.09834385</v>
+      </c>
+      <c r="D47">
+        <v>231542145.4408699</v>
       </c>
       <c r="E47">
-        <v>275414166</v>
+        <v>95156613.94893119</v>
       </c>
       <c r="F47">
-        <v>-117498553.32044274</v>
+        <v>-159361227.1667555</v>
+      </c>
+      <c r="G47">
+        <v>294730067.1667555</v>
+      </c>
+      <c r="H47">
+        <v>-125739198.58621466</v>
       </c>
     </row>
     <row r="48">
@@ -5496,16 +6380,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-19175042</v>
+        <v>-20311615.322504226</v>
       </c>
       <c r="C48">
-        <v>21239447.97196562</v>
+        <v>-20519864.677495774</v>
+      </c>
+      <c r="D48">
+        <v>22729055.72824542</v>
       </c>
       <c r="E48">
-        <v>16183936</v>
+        <v>-12672047.93255861</v>
       </c>
       <c r="F48">
-        <v>-13146854.898174116</v>
+        <v>-4298141.405323349</v>
+      </c>
+      <c r="G48">
+        <v>17318980.40532335</v>
+      </c>
+      <c r="H48">
+        <v>-14068896.612857763</v>
       </c>
     </row>
     <row r="49">
@@ -5513,10 +6406,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>176422994</v>
-      </c>
-      <c r="E49">
-        <v>-116997221</v>
+        <v>117829114.14543515</v>
+      </c>
+      <c r="C49">
+        <v>188796246.85456485</v>
+      </c>
+      <c r="F49">
+        <v>1668847.8174405545</v>
+      </c>
+      <c r="G49">
+        <v>-125202705.81744055</v>
       </c>
     </row>
     <row r="50">
@@ -5584,16 +6483,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-2125142</v>
+        <v>-4756700.2597330045</v>
       </c>
       <c r="C62">
-        <v>-1870416.8286386654</v>
+        <v>-2274186.740266995</v>
+      </c>
+      <c r="D62">
+        <v>-2001596.6699930169</v>
       </c>
       <c r="E62">
-        <v>-3210803</v>
+        <v>-3239346.5807817727</v>
       </c>
       <c r="F62">
-        <v>-5309246.997943129</v>
+        <v>-2989762.4952000906</v>
+      </c>
+      <c r="G62">
+        <v>-3435989.5047999094</v>
+      </c>
+      <c r="H62">
+        <v>-5681605.8049413245</v>
       </c>
     </row>
     <row r="63">
@@ -5617,16 +6525,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-45237009</v>
+        <v>-123049266.94582257</v>
       </c>
       <c r="C67">
-        <v>-35787987.36461815</v>
+        <v>-48409662.054177426</v>
+      </c>
+      <c r="D67">
+        <v>-38297942.59652172</v>
       </c>
       <c r="E67">
-        <v>-17051746</v>
+        <v>-66281521.073918566</v>
       </c>
       <c r="F67">
-        <v>-68086166.69183496</v>
+        <v>-21792486.595380086</v>
+      </c>
+      <c r="G67">
+        <v>-18247653.404619914</v>
+      </c>
+      <c r="H67">
+        <v>-72861322.90744779</v>
       </c>
     </row>
     <row r="68">
@@ -5678,8 +6595,11 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>101222107.442214</v>
+      <c r="D77">
+        <v>108321220.213503</v>
+      </c>
+      <c r="E77">
+        <v>-105651564.69118147</v>
       </c>
     </row>
     <row r="78">
@@ -5687,13 +6607,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-36516583</v>
+        <v>-92610472.43109441</v>
       </c>
       <c r="C78">
-        <v>-118663723.73450965</v>
+        <v>-39077637.56890559</v>
+      </c>
+      <c r="D78">
+        <v>-126986087.07922941</v>
       </c>
       <c r="E78">
-        <v>-14656991</v>
+        <v>39370043.94975677</v>
+      </c>
+      <c r="F78">
+        <v>-22618180.37775232</v>
+      </c>
+      <c r="G78">
+        <v>-15684944.622247683</v>
       </c>
     </row>
     <row r="79">
@@ -5791,10 +6720,16 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B97">
-        <v>-8720426</v>
-      </c>
-      <c r="E97">
-        <v>-2394755</v>
+        <v>-33288794.514728166</v>
+      </c>
+      <c r="C97">
+        <v>-9332024.485271832</v>
+      </c>
+      <c r="F97">
+        <v>-0.2176277688704431</v>
+      </c>
+      <c r="G97">
+        <v>-2562708.782372231</v>
       </c>
     </row>
     <row r="98">
@@ -5813,16 +6748,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>431579541</v>
+        <v>-62095370.872592986</v>
       </c>
       <c r="C101">
-        <v>-189381225.9798805</v>
+        <v>461847946.872593</v>
+      </c>
+      <c r="D101">
+        <v>-202663291.66660473</v>
       </c>
       <c r="E101">
-        <v>197186769</v>
+        <v>-361602525.1309775</v>
       </c>
       <c r="F101">
-        <v>126861306.27262017</v>
+        <v>-54595449.75563657</v>
+      </c>
+      <c r="G101">
+        <v>211016268.75563657</v>
+      </c>
+      <c r="H101">
+        <v>135758598.99156997</v>
       </c>
     </row>
     <row r="102">
@@ -5840,7 +6784,10 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>921308776</v>
+        <v>2635.761033654213</v>
+      </c>
+      <c r="C104">
+        <v>985923859.2389663</v>
       </c>
     </row>
     <row r="105">
@@ -5867,14 +6814,20 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>-111262550.23222604</v>
+      <c r="D109">
+        <v>-119065839.56574145</v>
       </c>
       <c r="E109">
-        <v>379679059</v>
+        <v>-198983979.95893645</v>
       </c>
       <c r="F109">
-        <v>147991680.40441412</v>
+        <v>57767142.29491764</v>
+      </c>
+      <c r="G109">
+        <v>406307475.70508236</v>
+      </c>
+      <c r="H109">
+        <v>158370931.09333378</v>
       </c>
     </row>
     <row r="110">
@@ -5882,7 +6835,10 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-470710796</v>
+        <v>-94938316.11401844</v>
+      </c>
+      <c r="C110">
+        <v>-503723633.88598156</v>
       </c>
     </row>
     <row r="111">
@@ -5924,17 +6880,23 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="B118">
-        <v>-19018439</v>
-      </c>
       <c r="C118">
-        <v>-470279171.93744904</v>
+        <v>-20352278.480391756</v>
+      </c>
+      <c r="D118">
+        <v>-503261738.2950828</v>
       </c>
       <c r="E118">
-        <v>-182492290</v>
+        <v>257045741.02217853</v>
       </c>
       <c r="F118">
-        <v>-203099711.80580986</v>
+        <v>-112362592.05055419</v>
+      </c>
+      <c r="G118">
+        <v>-195291206.9494458</v>
+      </c>
+      <c r="H118">
+        <v>-217343909.9791077</v>
       </c>
     </row>
     <row r="119">
@@ -5972,27 +6934,36 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>560640384</v>
+        <v>-72072223.93271339</v>
       </c>
       <c r="C125">
-        <v>-53354897.34983324</v>
+        <v>599960344.9327134</v>
+      </c>
+      <c r="D125">
+        <v>-57096890.50486857</v>
       </c>
       <c r="E125">
-        <v>59926999</v>
+        <v>78376357.24215823</v>
       </c>
       <c r="F125">
-        <v>-58711991.75667605</v>
+        <v>-77708851.02877618</v>
+      </c>
+      <c r="G125">
+        <v>64129920.02877618</v>
+      </c>
+      <c r="H125">
+        <v>-62829699.449588686</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
-      <c r="B126">
-        <v>-3667870</v>
-      </c>
-      <c r="E126">
-        <v>-3948945</v>
+      <c r="C126">
+        <v>-3925112.448496667</v>
+      </c>
+      <c r="G126">
+        <v>-4225900.366678392</v>
       </c>
     </row>
     <row r="127">
@@ -6000,16 +6971,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>556972514</v>
+        <v>-68147111.48421681</v>
       </c>
       <c r="C127">
-        <v>-54791757.77328317</v>
+        <v>596035232.4842168</v>
+      </c>
+      <c r="D127">
+        <v>-58634523.718378186</v>
       </c>
       <c r="E127">
-        <v>55978054</v>
+        <v>69005526.50840457</v>
       </c>
       <c r="F127">
-        <v>-61977373.69770683</v>
+        <v>-73482950.6620978</v>
+      </c>
+      <c r="G127">
+        <v>59904019.6620978</v>
+      </c>
+      <c r="H127">
+        <v>-66324095.73567192</v>
       </c>
     </row>
     <row r="128">
@@ -6017,10 +6997,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>40193162</v>
-      </c>
-      <c r="E128">
-        <v>43191166</v>
+        <v>114.18546371906996</v>
+      </c>
+      <c r="C128">
+        <v>43012069.81453628</v>
+      </c>
+      <c r="F128">
+        <v>9.128857895731926</v>
+      </c>
+      <c r="G128">
+        <v>46220335.871142104</v>
       </c>
     </row>
     <row r="129">
@@ -6028,22 +7014,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>597165676</v>
-      </c>
-      <c r="E129">
-        <v>99169220</v>
+        <v>-74633889.29875302</v>
+      </c>
+      <c r="C129">
+        <v>639047302.298753</v>
+      </c>
+      <c r="F129">
+        <v>-80088338.5332399</v>
+      </c>
+      <c r="G129">
+        <v>106124355.5332399</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6054,6 +7046,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6061,27 +7055,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6095,22 +7095,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>817959134.6673212</v>
+        <v>989719221.2053121</v>
       </c>
       <c r="C3">
-        <v>523453258.6673212</v>
+        <v>875325892.6418505</v>
       </c>
       <c r="D3">
-        <v>355767304.65454406</v>
-      </c>
-      <c r="F3">
-        <v>200346.13819520926</v>
+        <v>560165137.2053121</v>
+      </c>
+      <c r="E3">
+        <v>380718694.02886605</v>
       </c>
       <c r="H3">
-        <v>-8487238.333254138</v>
-      </c>
-      <c r="I3">
-        <v>1191126846.9908233</v>
+        <v>214397.21719642446</v>
+      </c>
+      <c r="J3">
+        <v>-9082482.431278622</v>
+      </c>
+      <c r="K3">
+        <v>1274665354.7869105</v>
       </c>
     </row>
     <row r="4">
@@ -6118,22 +7121,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>168899940.6003893</v>
+        <v>237831641.76733348</v>
       </c>
       <c r="C4">
-        <v>179144787.6003893</v>
+        <v>180745571.5172391</v>
       </c>
       <c r="D4">
-        <v>219281493.917515</v>
-      </c>
-      <c r="F4">
-        <v>183532916.36716783</v>
+        <v>191708930.76733348</v>
+      </c>
+      <c r="E4">
+        <v>234660585.43530288</v>
       </c>
       <c r="H4">
-        <v>339288753.8874561</v>
-      </c>
-      <c r="I4">
-        <v>340837304.469307</v>
+        <v>196404816.62154552</v>
+      </c>
+      <c r="J4">
+        <v>363084436.3400491</v>
+      </c>
+      <c r="K4">
+        <v>364741592.99117076</v>
       </c>
     </row>
     <row r="5">
@@ -6141,22 +7147,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>125909141.12431598</v>
+        <v>19059275.96803546</v>
       </c>
       <c r="C5">
-        <v>711041141.124316</v>
+        <v>134739654.6787581</v>
       </c>
       <c r="D5">
-        <v>883734159.9194901</v>
-      </c>
-      <c r="F5">
-        <v>220966430.73845646</v>
+        <v>760909310.9680355</v>
+      </c>
+      <c r="E5">
+        <v>945713984.4819294</v>
       </c>
       <c r="H5">
-        <v>292560894.4560973</v>
-      </c>
-      <c r="I5">
-        <v>1029399693.7487779</v>
+        <v>236463693.64001232</v>
+      </c>
+      <c r="J5">
+        <v>313079364.5284449</v>
+      </c>
+      <c r="K5">
+        <v>1101595627.0020432</v>
       </c>
     </row>
     <row r="6">
@@ -6164,22 +7173,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>125443145.26748002</v>
+        <v>135191830.95251393</v>
       </c>
       <c r="C6">
-        <v>122722629.26748002</v>
+        <v>134240976.66164875</v>
       </c>
       <c r="D6">
-        <v>116821909.22802244</v>
-      </c>
-      <c r="F6">
-        <v>114910571.43074161</v>
+        <v>131329659.95251392</v>
+      </c>
+      <c r="E6">
+        <v>125015098.72707006</v>
       </c>
       <c r="H6">
-        <v>116360559.18594567</v>
-      </c>
-      <c r="I6">
-        <v>112610996.60518172</v>
+        <v>122969711.13661861</v>
+      </c>
+      <c r="J6">
+        <v>124521392.35436058</v>
+      </c>
+      <c r="K6">
+        <v>120508857.8964398</v>
       </c>
     </row>
     <row r="7">
@@ -6192,22 +7204,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1718978.0308491774</v>
+        <v>4240593.54601337</v>
       </c>
       <c r="C8">
-        <v>4516318.030849177</v>
+        <v>1839536.8613332515</v>
       </c>
       <c r="D8">
-        <v>11478679.697443021</v>
-      </c>
-      <c r="F8">
-        <v>13249807.661751857</v>
+        <v>4833065.54601337</v>
+      </c>
+      <c r="E8">
+        <v>12283725.588076884</v>
       </c>
       <c r="H8">
-        <v>10357124.216558466</v>
-      </c>
-      <c r="I8">
-        <v>3833335.708073722</v>
+        <v>14179069.867069643</v>
+      </c>
+      <c r="J8">
+        <v>11083510.918609418</v>
+      </c>
+      <c r="K8">
+        <v>4102182.930972731</v>
       </c>
     </row>
     <row r="9">
@@ -6230,22 +7245,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>354096647.2690282</v>
+        <v>233727965.27290428</v>
       </c>
       <c r="C12">
-        <v>517570499.2690282</v>
+        <v>378930866.7337162</v>
       </c>
       <c r="D12">
-        <v>460582197.6531676</v>
-      </c>
-      <c r="F12">
-        <v>231821912.61112106</v>
+        <v>553869796.2729043</v>
+      </c>
+      <c r="E12">
+        <v>492884676.2738048</v>
       </c>
       <c r="H12">
-        <v>121232321.78043015</v>
-      </c>
-      <c r="I12">
-        <v>229180525.25102606</v>
+        <v>248080514.03790694</v>
+      </c>
+      <c r="J12">
+        <v>129734831.21826018</v>
+      </c>
+      <c r="K12">
+        <v>245253875.57787138</v>
       </c>
     </row>
     <row r="13">
@@ -6277,14 +7295,14 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>-6191176.884790843</v>
-      </c>
-      <c r="F18">
-        <v>-709858.0498766317</v>
+      <c r="D18">
+        <v>-6625388.975437339</v>
       </c>
       <c r="H18">
-        <v>-160389549.57516885</v>
+        <v>-759643.244781395</v>
+      </c>
+      <c r="J18">
+        <v>-171638312.60275543</v>
       </c>
     </row>
     <row r="19">
@@ -6297,41 +7315,47 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>42090548.165805794</v>
+        <v>57051975.29518736</v>
       </c>
       <c r="C20">
-        <v>37622274.165805794</v>
+        <v>45042527.28958575</v>
       </c>
       <c r="D20">
-        <v>293034036.2147163</v>
-      </c>
-      <c r="F20">
-        <v>16269535.20943006</v>
+        <v>40260875.29518736</v>
+      </c>
+      <c r="E20">
+        <v>313585689.61811787</v>
       </c>
       <c r="H20">
-        <v>195518861.0010632</v>
-      </c>
-      <c r="I20">
-        <v>229374775.18760282</v>
+        <v>17410583.03096586</v>
+      </c>
+      <c r="J20">
+        <v>209231383.67258453</v>
+      </c>
+      <c r="K20">
+        <v>245461749.04235545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="H21">
-        <v>9481577.847268665</v>
-      </c>
-      <c r="I21">
-        <v>454400060.9968935</v>
+      <c r="J21">
+        <v>10146558.967385558</v>
+      </c>
+      <c r="K21">
+        <v>486268961.55440396</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>-1485858.0669973562</v>
+      <c r="B22">
+        <v>-2323396.2585098483</v>
+      </c>
+      <c r="D22">
+        <v>-1590067.2585098485</v>
       </c>
     </row>
     <row r="23">
@@ -6364,22 +7388,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>532966479.9900167</v>
+        <v>745100133.7207181</v>
       </c>
       <c r="C28">
-        <v>-355830582.0099833</v>
+        <v>570345558.9320953</v>
       </c>
       <c r="D28">
-        <v>-854522924.2851053</v>
-      </c>
-      <c r="F28">
-        <v>-395061738.1257929</v>
+        <v>-380786409.27928185</v>
+      </c>
+      <c r="E28">
+        <v>-914454047.6181657</v>
       </c>
       <c r="H28">
-        <v>-13149448.107109128</v>
-      </c>
-      <c r="I28">
-        <v>-177332901.42032298</v>
+        <v>-422769003.87480474</v>
+      </c>
+      <c r="J28">
+        <v>-14071671.693946343</v>
+      </c>
+      <c r="K28">
+        <v>-189769969.73528016</v>
       </c>
     </row>
     <row r="29">
@@ -6397,22 +7424,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>481728096.42738354</v>
+        <v>384369237.21371305</v>
       </c>
       <c r="C31">
-        <v>-818870122.5726165</v>
+        <v>515513621.8234905</v>
       </c>
       <c r="D31">
-        <v>-536806014.15046424</v>
-      </c>
-      <c r="F31">
-        <v>352784285.872528</v>
+        <v>-876300771.786287</v>
+      </c>
+      <c r="E31">
+        <v>-574454375.0377917</v>
       </c>
       <c r="H31">
-        <v>461740239.8811898</v>
-      </c>
-      <c r="I31">
-        <v>63531409.10704379</v>
+        <v>377526464.1637426</v>
+      </c>
+      <c r="J31">
+        <v>494123936.65247005</v>
+      </c>
+      <c r="K31">
+        <v>67987121.88725121</v>
       </c>
     </row>
     <row r="32">
@@ -6425,22 +7455,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-3652478.4835466305</v>
+        <v>-30926291.5260354</v>
       </c>
       <c r="C33">
-        <v>-6416972.4835466305</v>
+        <v>-3908641.463202106</v>
       </c>
       <c r="D33">
-        <v>-8172215.599196331</v>
-      </c>
-      <c r="F33">
-        <v>14641697.389334267</v>
+        <v>-6867020.526035397</v>
+      </c>
+      <c r="E33">
+        <v>-8745365.888159659</v>
       </c>
       <c r="H33">
-        <v>11710723.221268585</v>
-      </c>
-      <c r="I33">
-        <v>37037600.35951319</v>
+        <v>15668578.409266708</v>
+      </c>
+      <c r="J33">
+        <v>12532043.255813405</v>
+      </c>
+      <c r="K33">
+        <v>39635195.967569694</v>
       </c>
     </row>
     <row r="34">
@@ -6463,22 +7496,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-251197735.4560698</v>
+        <v>-403586863.3856517</v>
       </c>
       <c r="C37">
-        <v>-204968915.4560698</v>
+        <v>-268815241.12708247</v>
       </c>
       <c r="D37">
-        <v>-456421475.4086951</v>
-      </c>
-      <c r="F37">
-        <v>-783406.9578840424</v>
+        <v>-219344208.38565174</v>
+      </c>
+      <c r="E37">
+        <v>-488432145.874277</v>
       </c>
       <c r="H37">
-        <v>-259411503.60883456</v>
-      </c>
-      <c r="I37">
-        <v>-87469739.56908073</v>
+        <v>-838350.4329841458</v>
+      </c>
+      <c r="J37">
+        <v>-277605073.81621337</v>
+      </c>
+      <c r="K37">
+        <v>-93604343.56979944</v>
       </c>
     </row>
     <row r="38">
@@ -6491,22 +7527,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>137332105.0192153</v>
+        <v>79083752.27072713</v>
       </c>
       <c r="C39">
-        <v>-48327159.98078472</v>
+        <v>146963756.8913766</v>
       </c>
       <c r="D39">
-        <v>2183034.9944699295</v>
-      </c>
-      <c r="F39">
-        <v>-308318853.46934295</v>
+        <v>-51716537.729272865</v>
+      </c>
+      <c r="E39">
+        <v>2336140.0028620698</v>
       </c>
       <c r="H39">
-        <v>22535854.325859312</v>
-      </c>
-      <c r="I39">
-        <v>171403543.7163595</v>
+        <v>-329942492.4707631</v>
+      </c>
+      <c r="J39">
+        <v>24116384.26441991</v>
+      </c>
+      <c r="K39">
+        <v>183424762.37094697</v>
       </c>
     </row>
     <row r="40">
@@ -6514,22 +7553,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>61883243.85936874</v>
+        <v>490333741.94042474</v>
       </c>
       <c r="C40">
-        <v>270739485.85936874</v>
+        <v>66223364.19386819</v>
       </c>
       <c r="D40">
-        <v>11363640.990566999</v>
-      </c>
-      <c r="F40">
-        <v>-851451.5548383975</v>
+        <v>289727532.94042474</v>
+      </c>
+      <c r="E40">
+        <v>12160618.754841775</v>
       </c>
       <c r="H40">
-        <v>-765953.7879021864</v>
-      </c>
-      <c r="I40">
-        <v>-131292236.33646747</v>
+        <v>-911167.2707015343</v>
+      </c>
+      <c r="J40">
+        <v>-819673.2021222255</v>
+      </c>
+      <c r="K40">
+        <v>-140500287.96964857</v>
       </c>
     </row>
     <row r="41">
@@ -6542,22 +7584,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>920907.8812591247</v>
+        <v>4784891.963296877</v>
       </c>
       <c r="C42">
-        <v>-1350670.1187408755</v>
+        <v>985494.8481404409</v>
       </c>
       <c r="D42">
-        <v>9483896.116742503</v>
-      </c>
-      <c r="F42">
-        <v>15938067.182422798</v>
+        <v>-1445398.0367031225</v>
+      </c>
+      <c r="E42">
+        <v>10149039.826404752</v>
       </c>
       <c r="H42">
-        <v>24227254.79249351</v>
-      </c>
-      <c r="I42">
-        <v>-16020705.98693878</v>
+        <v>17055867.820479985</v>
+      </c>
+      <c r="J42">
+        <v>25926409.436244145</v>
+      </c>
+      <c r="K42">
+        <v>-17144302.416126657</v>
       </c>
     </row>
     <row r="43">
@@ -6570,22 +7615,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>139896601.61390433</v>
+        <v>139572887.05875573</v>
       </c>
       <c r="C44">
-        <v>13594.613904327707</v>
+        <v>149708111.92793497</v>
       </c>
       <c r="D44">
-        <v>-37894.54121112528</v>
-      </c>
-      <c r="F44">
-        <v>45461.73581265101</v>
+        <v>14548.058755730863</v>
+      </c>
+      <c r="E44">
+        <v>-40552.23752146553</v>
       </c>
       <c r="H44">
-        <v>18522677.002251115</v>
-      </c>
-      <c r="I44">
-        <v>-249719238.37321588</v>
+        <v>48650.149860410325</v>
+      </c>
+      <c r="J44">
+        <v>19821746.703405187</v>
+      </c>
+      <c r="K44">
+        <v>-267233051.10808623</v>
       </c>
     </row>
     <row r="45">
@@ -6603,22 +7651,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-20150662.981541693</v>
+        <v>112243250.38980108</v>
       </c>
       <c r="C47">
-        <v>431784798.0184583</v>
+        <v>-21563909.87529826</v>
       </c>
       <c r="D47">
-        <v>97918815.7028346</v>
-      </c>
-      <c r="F47">
-        <v>-454549359.7472815</v>
+        <v>462067599.3898011</v>
+      </c>
+      <c r="E47">
+        <v>104786255.36271653</v>
       </c>
       <c r="H47">
-        <v>-229007539.27242652</v>
-      </c>
-      <c r="I47">
-        <v>96090205.78010346</v>
+        <v>-486428731.22554624</v>
+      </c>
+      <c r="J47">
+        <v>-245068757.3981059</v>
+      </c>
+      <c r="K47">
+        <v>102829397.68478449</v>
       </c>
     </row>
     <row r="48">
@@ -6626,22 +7677,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-13793597.889956087</v>
+        <v>-30774472.20431319</v>
       </c>
       <c r="C48">
-        <v>21565380.110043913</v>
+        <v>-14760998.287132312</v>
       </c>
       <c r="D48">
-        <v>-12820922.76009582</v>
-      </c>
-      <c r="F48">
-        <v>-13968178.57654381</v>
+        <v>23077846.79568681</v>
+      </c>
+      <c r="E48">
+        <v>-13720105.545416372</v>
       </c>
       <c r="H48">
-        <v>19436532.257328004</v>
-      </c>
-      <c r="I48">
-        <v>66789185.95990758</v>
+        <v>-14947823.018159466</v>
+      </c>
+      <c r="J48">
+        <v>20799694.296375055</v>
+      </c>
+      <c r="K48">
+        <v>71473379.70980215</v>
       </c>
     </row>
     <row r="49">
@@ -6649,13 +7703,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>827775561.7147219</v>
+        <v>1001991051.4560869</v>
       </c>
       <c r="C49">
-        <v>534355346.7147219</v>
-      </c>
-      <c r="F49">
-        <v>9437608.979831355</v>
+        <v>885830785.1280923</v>
+      </c>
+      <c r="D49">
+        <v>571831832.4560869</v>
+      </c>
+      <c r="H49">
+        <v>10099506.38675307</v>
       </c>
     </row>
     <row r="50">
@@ -6723,22 +7780,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-9816427.04740073</v>
+        <v>-12271830.25077479</v>
       </c>
       <c r="C62">
-        <v>-10902088.04740073</v>
+        <v>-10504892.486241875</v>
       </c>
       <c r="D62">
-        <v>-14340918.216705194</v>
-      </c>
-      <c r="F62">
-        <v>-9237262.841636145</v>
+        <v>-11666695.25077479</v>
+      </c>
+      <c r="E62">
+        <v>-15346704.385723097</v>
       </c>
       <c r="H62">
-        <v>-8487238.333254138</v>
-      </c>
-      <c r="I62">
-        <v>-1777249.8069386615</v>
+        <v>-9885109.169556646</v>
+      </c>
+      <c r="J62">
+        <v>-9082482.431278622</v>
+      </c>
+      <c r="K62">
+        <v>-1901895.4710235745</v>
       </c>
     </row>
     <row r="63">
@@ -6762,22 +7822,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-163326844.97374973</v>
+        <v>-276038392.6704403</v>
       </c>
       <c r="C67">
-        <v>-135141581.97374973</v>
+        <v>-174781612.3199978</v>
       </c>
       <c r="D67">
-        <v>-167439761.30096653</v>
-      </c>
-      <c r="F67">
-        <v>-248575829.3940641</v>
+        <v>-144619603.6704403</v>
+      </c>
+      <c r="E67">
+        <v>-179182983.98136634</v>
       </c>
       <c r="H67">
-        <v>-219225512.27522406</v>
-      </c>
-      <c r="I67">
-        <v>-611834733.4435409</v>
+        <v>-266009450.26678282</v>
+      </c>
+      <c r="J67">
+        <v>-234600677.57568857</v>
+      </c>
+      <c r="K67">
+        <v>-654745159.6326703</v>
       </c>
     </row>
     <row r="68">
@@ -6829,14 +7892,17 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>3266272.7044540634</v>
-      </c>
-      <c r="H77">
-        <v>-137762792.02991784</v>
-      </c>
-      <c r="I77">
-        <v>-593929776.8894755</v>
+      <c r="B77">
+        <v>5519655.522321543</v>
+      </c>
+      <c r="D77">
+        <v>3495349.522321543</v>
+      </c>
+      <c r="J77">
+        <v>-147424649.71121874</v>
+      </c>
+      <c r="K77">
+        <v>-635584456.5924442</v>
       </c>
     </row>
     <row r="78">
@@ -6844,13 +7910,16 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-139526320.0918133</v>
+        <v>-219304153.12947264</v>
       </c>
       <c r="C78">
-        <v>-117666728.0918133</v>
-      </c>
-      <c r="F78">
-        <v>-205686691.04253715</v>
+        <v>-149311861.07613057</v>
+      </c>
+      <c r="D78">
+        <v>-125919168.12947264</v>
+      </c>
+      <c r="H78">
+        <v>-220112324.4556515</v>
       </c>
     </row>
     <row r="79">
@@ -6948,13 +8017,16 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B97">
-        <v>-27066797.586390503</v>
+        <v>-62253895.063289195</v>
       </c>
       <c r="C97">
-        <v>-20741126.586390503</v>
-      </c>
-      <c r="F97">
-        <v>-42889138.351526946</v>
+        <v>-28965100.766188793</v>
+      </c>
+      <c r="D97">
+        <v>-22195785.063289195</v>
+      </c>
+      <c r="H97">
+        <v>-45897125.81113132</v>
       </c>
     </row>
     <row r="98">
@@ -6973,22 +8045,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-146723043.58504438</v>
+        <v>-164513240.79758215</v>
       </c>
       <c r="C101">
-        <v>-381115815.5850444</v>
+        <v>-157013319.68062586</v>
       </c>
       <c r="D101">
-        <v>-64873283.3325437</v>
-      </c>
-      <c r="F101">
-        <v>239490842.95457146</v>
+        <v>-407844997.7975822</v>
+      </c>
+      <c r="E101">
+        <v>-69423107.13940752</v>
       </c>
       <c r="H101">
-        <v>375060116.9567418</v>
-      </c>
-      <c r="I101">
-        <v>-464020876.0264669</v>
+        <v>256287297.25479603</v>
+      </c>
+      <c r="J101">
+        <v>401364588.71266514</v>
+      </c>
+      <c r="K101">
+        <v>-496564522.9666847</v>
       </c>
     </row>
     <row r="102">
@@ -7030,31 +8105,34 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>136454683.68398374</v>
+      <c r="B109">
+        <v>-318049819.5246779</v>
       </c>
       <c r="D109">
-        <v>395708914.3206239</v>
-      </c>
-      <c r="F109">
-        <v>471312755.56569254</v>
+        <v>146024798.4753221</v>
+      </c>
+      <c r="E109">
+        <v>423461569.1343973</v>
       </c>
       <c r="H109">
-        <v>360719228.0512173</v>
-      </c>
-      <c r="I109">
-        <v>64032091.08608882</v>
+        <v>504367811.29270303</v>
+      </c>
+      <c r="J109">
+        <v>386017915.69383353</v>
+      </c>
+      <c r="K109">
+        <v>68522918.70357448</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="H110">
-        <v>-253827796.32465953</v>
-      </c>
-      <c r="I110">
-        <v>-234840350.77544087</v>
+      <c r="J110">
+        <v>-271629758.7232911</v>
+      </c>
+      <c r="K110">
+        <v>-251310647.38881338</v>
       </c>
     </row>
     <row r="111">
@@ -7096,34 +8174,34 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="B118">
-        <v>-354096648.2690282</v>
-      </c>
       <c r="C118">
-        <v>-517570499.2690282</v>
+        <v>-378930867.8038502</v>
       </c>
       <c r="D118">
-        <v>-250391039.137389</v>
-      </c>
-      <c r="F118">
-        <v>-231821912.61112106</v>
+        <v>-553869796.2729043</v>
+      </c>
+      <c r="E118">
+        <v>-267951967.95692918</v>
       </c>
       <c r="H118">
-        <v>-2204302.015633074</v>
-      </c>
-      <c r="I118">
-        <v>-240563.95554196043</v>
+        <v>-248080514.03790694</v>
+      </c>
+      <c r="J118">
+        <v>-2358898.5656001098</v>
+      </c>
+      <c r="K118">
+        <v>-257435.6715361634</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="H119">
-        <v>36696.60534209229</v>
-      </c>
-      <c r="I119">
-        <v>68264.68898379078</v>
+      <c r="J119">
+        <v>39270.285600584466</v>
+      </c>
+      <c r="K119">
+        <v>73052.36568445187</v>
       </c>
     </row>
     <row r="120">
@@ -7145,11 +8223,11 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H123">
-        <v>-81462720.24530622</v>
-      </c>
-      <c r="I123">
-        <v>-17904956.55406537</v>
+      <c r="J123">
+        <v>-87176027.86446983</v>
+      </c>
+      <c r="K123">
+        <v>-19160703.04022606</v>
       </c>
     </row>
     <row r="124">
@@ -7162,36 +8240,39 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>507909246.10852706</v>
+        <v>549167587.7372897</v>
       </c>
       <c r="C125">
-        <v>7195861.108527065</v>
+        <v>543530960.6412269</v>
       </c>
       <c r="D125">
-        <v>1838766.7016842589</v>
-      </c>
-      <c r="F125">
-        <v>-8884640.30129743</v>
+        <v>7700535.737289656</v>
+      </c>
+      <c r="E125">
+        <v>1967726.7925695404</v>
       </c>
       <c r="H125">
-        <v>15927332.671224333</v>
-      </c>
-      <c r="I125">
-        <v>115271237.52081539</v>
+        <v>-9507755.794790361</v>
+      </c>
+      <c r="J125">
+        <v>17044380.454915334</v>
+      </c>
+      <c r="K125">
+        <v>123355672.18755533</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
-      <c r="B126">
-        <v>-9912474.403552208</v>
-      </c>
       <c r="C126">
-        <v>-10193549.403552208</v>
-      </c>
-      <c r="F126">
-        <v>-23110537.720029484</v>
+        <v>-10607676.02908155</v>
+      </c>
+      <c r="D126">
+        <v>-10908463.947263274</v>
+      </c>
+      <c r="H126">
+        <v>-24731372.512204498</v>
       </c>
     </row>
     <row r="127">
@@ -7199,22 +8280,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>497996771.7049749</v>
+        <v>538259123.7900264</v>
       </c>
       <c r="C127">
-        <v>-2997688.2950251433</v>
+        <v>532923284.6121454</v>
       </c>
       <c r="D127">
-        <v>-10183304.219448805</v>
-      </c>
-      <c r="F127">
-        <v>-31995178.021326914</v>
+        <v>-3207928.2099736193</v>
+      </c>
+      <c r="E127">
+        <v>-10897500.227267355</v>
       </c>
       <c r="H127">
-        <v>-65789549.11705205</v>
-      </c>
-      <c r="I127">
-        <v>40523553.93917237</v>
+        <v>-34239128.306994855</v>
+      </c>
+      <c r="J127">
+        <v>-70403634.32191542</v>
+      </c>
+      <c r="K127">
+        <v>43365633.466827236</v>
       </c>
     </row>
     <row r="128">
@@ -7222,13 +8306,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>40192920.69480089</v>
+        <v>43011916.64224061</v>
       </c>
       <c r="C128">
-        <v>43190924.69480089</v>
-      </c>
-      <c r="F128">
-        <v>75186102.7161278</v>
+        <v>43011811.58563479</v>
+      </c>
+      <c r="D128">
+        <v>46220077.64224061</v>
+      </c>
+      <c r="H128">
+        <v>80459205.94923547</v>
       </c>
     </row>
     <row r="129">
@@ -7236,18 +8323,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>538189692.3997757</v>
+        <v>581389545.432267</v>
       </c>
       <c r="C129">
-        <v>40193236.39977574</v>
-      </c>
-      <c r="F129">
-        <v>43190924.69480089</v>
+        <v>575935096.1977801</v>
+      </c>
+      <c r="D129">
+        <v>43012149.43226699</v>
+      </c>
+      <c r="H129">
+        <v>46220077.64224061</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>